--- a/excel/comuni_solare_2014.xlsx
+++ b/excel/comuni_solare_2014.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="246">
   <si>
     <t>Codice ISTAT comune</t>
   </si>
@@ -48,6 +48,711 @@
   </si>
   <si>
     <t>Azimuth</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>46.00</t>
+  </si>
+  <si>
+    <t>45.25</t>
+  </si>
+  <si>
+    <t>44.77</t>
+  </si>
+  <si>
+    <t>43.28</t>
+  </si>
+  <si>
+    <t>47.57</t>
+  </si>
+  <si>
+    <t>44.46</t>
+  </si>
+  <si>
+    <t>46.40</t>
+  </si>
+  <si>
+    <t>46.45</t>
+  </si>
+  <si>
+    <t>44.45</t>
+  </si>
+  <si>
+    <t>42.56</t>
+  </si>
+  <si>
+    <t>43.07</t>
+  </si>
+  <si>
+    <t>43.21</t>
+  </si>
+  <si>
+    <t>43.39</t>
+  </si>
+  <si>
+    <t>43.37</t>
+  </si>
+  <si>
+    <t>46.72</t>
+  </si>
+  <si>
+    <t>45.61</t>
+  </si>
+  <si>
+    <t>42.67</t>
+  </si>
+  <si>
+    <t>44.83</t>
+  </si>
+  <si>
+    <t>40.65</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>64.52</t>
+  </si>
+  <si>
+    <t>68.83</t>
+  </si>
+  <si>
+    <t>70.72</t>
+  </si>
+  <si>
+    <t>72.35</t>
+  </si>
+  <si>
+    <t>67.81</t>
+  </si>
+  <si>
+    <t>61.84</t>
+  </si>
+  <si>
+    <t>68.12</t>
+  </si>
+  <si>
+    <t>63.87</t>
+  </si>
+  <si>
+    <t>65.27</t>
+  </si>
+  <si>
+    <t>66.30</t>
+  </si>
+  <si>
+    <t>64.53</t>
+  </si>
+  <si>
+    <t>68.53</t>
+  </si>
+  <si>
+    <t>70.00</t>
+  </si>
+  <si>
+    <t>68.59</t>
+  </si>
+  <si>
+    <t>63.64</t>
+  </si>
+  <si>
+    <t>67.57</t>
+  </si>
+  <si>
+    <t>62.51</t>
+  </si>
+  <si>
+    <t>69.36</t>
+  </si>
+  <si>
+    <t>68.54</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>120.45</t>
+  </si>
+  <si>
+    <t>123.08</t>
+  </si>
+  <si>
+    <t>124.09</t>
+  </si>
+  <si>
+    <t>123.88</t>
+  </si>
+  <si>
+    <t>121.85</t>
+  </si>
+  <si>
+    <t>118.75</t>
+  </si>
+  <si>
+    <t>121.17</t>
+  </si>
+  <si>
+    <t>121.47</t>
+  </si>
+  <si>
+    <t>119.12</t>
+  </si>
+  <si>
+    <t>121.50</t>
+  </si>
+  <si>
+    <t>119.85</t>
+  </si>
+  <si>
+    <t>121.18</t>
+  </si>
+  <si>
+    <t>123.77</t>
+  </si>
+  <si>
+    <t>122.61</t>
+  </si>
+  <si>
+    <t>119.59</t>
+  </si>
+  <si>
+    <t>120.39</t>
+  </si>
+  <si>
+    <t>117.05</t>
+  </si>
+  <si>
+    <t>121.95</t>
+  </si>
+  <si>
+    <t>121.34</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>142.28</t>
+  </si>
+  <si>
+    <t>157.66</t>
+  </si>
+  <si>
+    <t>162.33</t>
+  </si>
+  <si>
+    <t>164.50</t>
+  </si>
+  <si>
+    <t>159.23</t>
+  </si>
+  <si>
+    <t>145.83</t>
+  </si>
+  <si>
+    <t>147.38</t>
+  </si>
+  <si>
+    <t>143.50</t>
+  </si>
+  <si>
+    <t>146.36</t>
+  </si>
+  <si>
+    <t>156.10</t>
+  </si>
+  <si>
+    <t>150.87</t>
+  </si>
+  <si>
+    <t>159.27</t>
+  </si>
+  <si>
+    <t>163.95</t>
+  </si>
+  <si>
+    <t>157.63</t>
+  </si>
+  <si>
+    <t>143.10</t>
+  </si>
+  <si>
+    <t>153.34</t>
+  </si>
+  <si>
+    <t>147.76</t>
+  </si>
+  <si>
+    <t>152.89</t>
+  </si>
+  <si>
+    <t>161.64</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>192.13</t>
+  </si>
+  <si>
+    <t>198.24</t>
+  </si>
+  <si>
+    <t>201.90</t>
+  </si>
+  <si>
+    <t>200.75</t>
+  </si>
+  <si>
+    <t>202.00</t>
+  </si>
+  <si>
+    <t>192.14</t>
+  </si>
+  <si>
+    <t>195.71</t>
+  </si>
+  <si>
+    <t>195.11</t>
+  </si>
+  <si>
+    <t>194.62</t>
+  </si>
+  <si>
+    <t>196.55</t>
+  </si>
+  <si>
+    <t>194.12</t>
+  </si>
+  <si>
+    <t>197.18</t>
+  </si>
+  <si>
+    <t>200.67</t>
+  </si>
+  <si>
+    <t>196.76</t>
+  </si>
+  <si>
+    <t>195.62</t>
+  </si>
+  <si>
+    <t>195.30</t>
+  </si>
+  <si>
+    <t>191.33</t>
+  </si>
+  <si>
+    <t>195.79</t>
+  </si>
+  <si>
+    <t>200.00</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>217.27</t>
+  </si>
+  <si>
+    <t>220.35</t>
+  </si>
+  <si>
+    <t>220.38</t>
+  </si>
+  <si>
+    <t>219.46</t>
+  </si>
+  <si>
+    <t>219.69</t>
+  </si>
+  <si>
+    <t>214.00</t>
+  </si>
+  <si>
+    <t>219.44</t>
+  </si>
+  <si>
+    <t>218.35</t>
+  </si>
+  <si>
+    <t>218.45</t>
+  </si>
+  <si>
+    <t>217.43</t>
+  </si>
+  <si>
+    <t>216.25</t>
+  </si>
+  <si>
+    <t>218.58</t>
+  </si>
+  <si>
+    <t>218.12</t>
+  </si>
+  <si>
+    <t>214.91</t>
+  </si>
+  <si>
+    <t>217.12</t>
+  </si>
+  <si>
+    <t>215.48</t>
+  </si>
+  <si>
+    <t>216.38</t>
+  </si>
+  <si>
+    <t>216.49</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>197.09</t>
+  </si>
+  <si>
+    <t>212.03</t>
+  </si>
+  <si>
+    <t>211.38</t>
+  </si>
+  <si>
+    <t>209.29</t>
+  </si>
+  <si>
+    <t>203.86</t>
+  </si>
+  <si>
+    <t>204.37</t>
+  </si>
+  <si>
+    <t>200.97</t>
+  </si>
+  <si>
+    <t>194.52</t>
+  </si>
+  <si>
+    <t>198.07</t>
+  </si>
+  <si>
+    <t>207.05</t>
+  </si>
+  <si>
+    <t>198.67</t>
+  </si>
+  <si>
+    <t>209.85</t>
+  </si>
+  <si>
+    <t>206.91</t>
+  </si>
+  <si>
+    <t>203.65</t>
+  </si>
+  <si>
+    <t>195.03</t>
+  </si>
+  <si>
+    <t>209.61</t>
+  </si>
+  <si>
+    <t>205.68</t>
+  </si>
+  <si>
+    <t>207.22</t>
+  </si>
+  <si>
+    <t>205.36</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>199.95</t>
+  </si>
+  <si>
+    <t>204.49</t>
+  </si>
+  <si>
+    <t>203.88</t>
+  </si>
+  <si>
+    <t>200.40</t>
+  </si>
+  <si>
+    <t>201.46</t>
+  </si>
+  <si>
+    <t>198.43</t>
+  </si>
+  <si>
+    <t>201.73</t>
+  </si>
+  <si>
+    <t>185.91</t>
+  </si>
+  <si>
+    <t>192.69</t>
+  </si>
+  <si>
+    <t>197.49</t>
+  </si>
+  <si>
+    <t>199.04</t>
+  </si>
+  <si>
+    <t>203.55</t>
+  </si>
+  <si>
+    <t>195.12</t>
+  </si>
+  <si>
+    <t>193.32</t>
+  </si>
+  <si>
+    <t>200.82</t>
+  </si>
+  <si>
+    <t>195.81</t>
+  </si>
+  <si>
+    <t>202.35</t>
+  </si>
+  <si>
+    <t>202.21</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>139.65</t>
+  </si>
+  <si>
+    <t>148.30</t>
+  </si>
+  <si>
+    <t>145.64</t>
+  </si>
+  <si>
+    <t>142.79</t>
+  </si>
+  <si>
+    <t>144.55</t>
+  </si>
+  <si>
+    <t>140.11</t>
+  </si>
+  <si>
+    <t>142.36</t>
+  </si>
+  <si>
+    <t>137.55</t>
+  </si>
+  <si>
+    <t>139.73</t>
+  </si>
+  <si>
+    <t>140.63</t>
+  </si>
+  <si>
+    <t>139.28</t>
+  </si>
+  <si>
+    <t>142.19</t>
+  </si>
+  <si>
+    <t>141.82</t>
+  </si>
+  <si>
+    <t>139.11</t>
+  </si>
+  <si>
+    <t>138.61</t>
+  </si>
+  <si>
+    <t>144.59</t>
+  </si>
+  <si>
+    <t>140.68</t>
+  </si>
+  <si>
+    <t>145.30</t>
+  </si>
+  <si>
+    <t>141.90</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>106.28</t>
+  </si>
+  <si>
+    <t>105.33</t>
+  </si>
+  <si>
+    <t>105.71</t>
+  </si>
+  <si>
+    <t>104.42</t>
+  </si>
+  <si>
+    <t>107.29</t>
+  </si>
+  <si>
+    <t>95.60</t>
+  </si>
+  <si>
+    <t>106.77</t>
+  </si>
+  <si>
+    <t>100.19</t>
+  </si>
+  <si>
+    <t>102.83</t>
+  </si>
+  <si>
+    <t>97.37</t>
+  </si>
+  <si>
+    <t>97.61</t>
+  </si>
+  <si>
+    <t>105.13</t>
+  </si>
+  <si>
+    <t>98.90</t>
+  </si>
+  <si>
+    <t>94.12</t>
+  </si>
+  <si>
+    <t>102.91</t>
+  </si>
+  <si>
+    <t>104.27</t>
+  </si>
+  <si>
+    <t>96.05</t>
+  </si>
+  <si>
+    <t>103.45</t>
+  </si>
+  <si>
+    <t>100.72</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>49.14</t>
+  </si>
+  <si>
+    <t>49.83</t>
+  </si>
+  <si>
+    <t>50.20</t>
+  </si>
+  <si>
+    <t>47.96</t>
+  </si>
+  <si>
+    <t>50.74</t>
+  </si>
+  <si>
+    <t>46.94</t>
+  </si>
+  <si>
+    <t>50.97</t>
+  </si>
+  <si>
+    <t>47.56</t>
+  </si>
+  <si>
+    <t>46.10</t>
+  </si>
+  <si>
+    <t>46.68</t>
+  </si>
+  <si>
+    <t>44.12</t>
+  </si>
+  <si>
+    <t>48.49</t>
+  </si>
+  <si>
+    <t>45.37</t>
+  </si>
+  <si>
+    <t>45.34</t>
+  </si>
+  <si>
+    <t>49.38</t>
+  </si>
+  <si>
+    <t>48.53</t>
+  </si>
+  <si>
+    <t>46.31</t>
+  </si>
+  <si>
+    <t>48.82</t>
+  </si>
+  <si>
+    <t>44.34</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>46.29</t>
+  </si>
+  <si>
+    <t>48.69</t>
+  </si>
+  <si>
+    <t>48.06</t>
+  </si>
+  <si>
+    <t>47.08</t>
+  </si>
+  <si>
+    <t>45.94</t>
+  </si>
+  <si>
+    <t>46.55</t>
+  </si>
+  <si>
+    <t>43.85</t>
+  </si>
+  <si>
+    <t>45.80</t>
+  </si>
+  <si>
+    <t>44.43</t>
+  </si>
+  <si>
+    <t>48.30</t>
+  </si>
+  <si>
+    <t>46.53</t>
+  </si>
+  <si>
+    <t>46.25</t>
+  </si>
+  <si>
+    <t>47.83</t>
+  </si>
+  <si>
+    <t>48.65</t>
+  </si>
+  <si>
+    <t>46.04</t>
   </si>
 </sst>
 </file>
@@ -439,23 +1144,23 @@
       <c r="A2">
         <v>49001</v>
       </c>
-      <c r="B2">
-        <v>2014</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>45.99</v>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>74.049999999999997</v>
+        <v>74.12</v>
       </c>
       <c r="F2">
-        <v>70.68000000000001</v>
+        <v>70.72</v>
       </c>
       <c r="G2">
-        <v>59.15</v>
+        <v>59.26</v>
       </c>
       <c r="H2">
         <v>0.58</v>
@@ -474,23 +1179,23 @@
       <c r="A3">
         <v>49002</v>
       </c>
-      <c r="B3">
-        <v>2014</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>46.0</v>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>73.76000000000001</v>
+        <v>71.52</v>
       </c>
       <c r="F3">
-        <v>69.98999999999999</v>
+        <v>68.19</v>
       </c>
       <c r="G3">
-        <v>58.8</v>
+        <v>56.27</v>
       </c>
       <c r="H3">
         <v>0.6</v>
@@ -499,7 +1204,7 @@
         <v>10.6</v>
       </c>
       <c r="J3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -509,26 +1214,26 @@
       <c r="A4">
         <v>49003</v>
       </c>
-      <c r="B4">
-        <v>2014</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>44.94</v>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>70.55</v>
+        <v>69.060000000000002</v>
       </c>
       <c r="F4">
-        <v>67.31999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="G4">
-        <v>55.49</v>
+        <v>52.44</v>
       </c>
       <c r="H4">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="I4">
         <v>13.3</v>
@@ -544,32 +1249,32 @@
       <c r="A5">
         <v>49004</v>
       </c>
-      <c r="B5">
-        <v>2014</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>41.85</v>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>61.34</v>
+        <v>66.69</v>
       </c>
       <c r="F5">
-        <v>59.4</v>
+        <v>63.9</v>
       </c>
       <c r="G5">
-        <v>42.89</v>
+        <v>50.69</v>
       </c>
       <c r="H5">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="I5">
         <v>13.3</v>
       </c>
       <c r="J5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -579,23 +1284,23 @@
       <c r="A6">
         <v>49005</v>
       </c>
-      <c r="B6">
-        <v>2014</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>47.45</v>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>76.060000000000002</v>
+        <v>77.060000000000002</v>
       </c>
       <c r="F6">
-        <v>72.43000000000001</v>
+        <v>73.23</v>
       </c>
       <c r="G6">
-        <v>59.24</v>
+        <v>61.56</v>
       </c>
       <c r="H6">
         <v>0.57</v>
@@ -604,7 +1309,7 @@
         <v>13.2</v>
       </c>
       <c r="J6">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -614,17 +1319,17 @@
       <c r="A7">
         <v>49006</v>
       </c>
-      <c r="B7">
-        <v>2014</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>44.46</v>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
       </c>
       <c r="E7">
-        <v>69.34</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="F7">
         <v>66.68000000000001</v>
@@ -649,29 +1354,29 @@
       <c r="A8">
         <v>49007</v>
       </c>
-      <c r="B8">
-        <v>2014</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>45.66</v>
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
       </c>
       <c r="E8">
-        <v>74.7</v>
+        <v>76.53</v>
       </c>
       <c r="F8">
-        <v>71.0</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="G8">
-        <v>60.95</v>
+        <v>63.43</v>
       </c>
       <c r="H8">
         <v>0.57</v>
       </c>
       <c r="I8">
-        <v>9.9</v>
+        <v>10.3</v>
       </c>
       <c r="J8">
         <v>36</v>
@@ -684,23 +1389,23 @@
       <c r="A9">
         <v>49008</v>
       </c>
-      <c r="B9">
-        <v>2014</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>46.45</v>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
       </c>
       <c r="E9">
-        <v>78.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="F9">
         <v>74.12</v>
       </c>
       <c r="G9">
-        <v>65.98999999999999</v>
+        <v>65.98</v>
       </c>
       <c r="H9">
         <v>0.54</v>
@@ -719,26 +1424,26 @@
       <c r="A10">
         <v>49009</v>
       </c>
-      <c r="B10">
-        <v>2014</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>45.25</v>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
       </c>
       <c r="E10">
-        <v>74.75</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="F10">
-        <v>71.0</v>
+        <v>69.2</v>
       </c>
       <c r="G10">
-        <v>61.53</v>
+        <v>59.4</v>
       </c>
       <c r="H10">
-        <v>0.56</v>
+        <v>0.57</v>
       </c>
       <c r="I10">
         <v>9.5</v>
@@ -754,23 +1459,23 @@
       <c r="A11">
         <v>49010</v>
       </c>
-      <c r="B11">
-        <v>2014</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>42.74</v>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
       </c>
       <c r="E11">
-        <v>62.62</v>
+        <v>62.049999999999997</v>
       </c>
       <c r="F11">
-        <v>60.75</v>
+        <v>60.21</v>
       </c>
       <c r="G11">
-        <v>43.52</v>
+        <v>42.72</v>
       </c>
       <c r="H11">
         <v>0.63</v>
@@ -789,26 +1494,26 @@
       <c r="A12">
         <v>49011</v>
       </c>
-      <c r="B12">
-        <v>2014</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>42.5</v>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
       </c>
       <c r="E12">
-        <v>63.19</v>
+        <v>65.33</v>
       </c>
       <c r="F12">
-        <v>61.3</v>
+        <v>62.96</v>
       </c>
       <c r="G12">
-        <v>45.0</v>
+        <v>47.58</v>
       </c>
       <c r="H12">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="I12">
         <v>12.3</v>
@@ -824,23 +1529,23 @@
       <c r="A13">
         <v>49012</v>
       </c>
-      <c r="B13">
-        <v>2014</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>43.21</v>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
       </c>
       <c r="E13">
-        <v>68.079999999999998</v>
+        <v>68.099999999999994</v>
       </c>
       <c r="F13">
-        <v>64.90000000000001</v>
+        <v>64.91</v>
       </c>
       <c r="G13">
-        <v>53.95</v>
+        <v>53.97</v>
       </c>
       <c r="H13">
         <v>0.6</v>
@@ -859,23 +1564,23 @@
       <c r="A14">
         <v>49013</v>
       </c>
-      <c r="B14">
-        <v>2014</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>43.39</v>
+      <c r="B14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
       </c>
       <c r="E14">
-        <v>66.090000000000003</v>
+        <v>66.16</v>
       </c>
       <c r="F14">
-        <v>63.59</v>
+        <v>63.6</v>
       </c>
       <c r="G14">
-        <v>49.6</v>
+        <v>49.61</v>
       </c>
       <c r="H14">
         <v>0.61</v>
@@ -894,23 +1599,23 @@
       <c r="A15">
         <v>49014</v>
       </c>
-      <c r="B15">
-        <v>2014</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>43.29</v>
+      <c r="B15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>26</v>
       </c>
       <c r="E15">
-        <v>66.33</v>
+        <v>67.079999999999998</v>
       </c>
       <c r="F15">
-        <v>63.74</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="G15">
-        <v>50.17</v>
+        <v>51.98</v>
       </c>
       <c r="H15">
         <v>0.61</v>
@@ -929,29 +1634,29 @@
       <c r="A16">
         <v>49017</v>
       </c>
-      <c r="B16">
-        <v>2014</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>46.26</v>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
       </c>
       <c r="E16">
-        <v>76.019999999999996</v>
+        <v>76.25</v>
       </c>
       <c r="F16">
-        <v>72.20999999999999</v>
+        <v>72.81</v>
       </c>
       <c r="G16">
-        <v>62.34</v>
+        <v>61.78</v>
       </c>
       <c r="H16">
-        <v>0.57</v>
+        <v>0.56</v>
       </c>
       <c r="I16">
-        <v>11.3</v>
+        <v>9.3</v>
       </c>
       <c r="J16">
         <v>36</v>
@@ -964,29 +1669,29 @@
       <c r="A17">
         <v>49018</v>
       </c>
-      <c r="B17">
-        <v>2014</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>45.7</v>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
       </c>
       <c r="E17">
-        <v>74.010000000000005</v>
+        <v>72.86</v>
       </c>
       <c r="F17">
-        <v>70.5</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="G17">
-        <v>59.93</v>
+        <v>57.88</v>
       </c>
       <c r="H17">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="I17">
-        <v>11.0</v>
+        <v>11.5</v>
       </c>
       <c r="J17">
         <v>36</v>
@@ -999,32 +1704,32 @@
       <c r="A18">
         <v>49019</v>
       </c>
-      <c r="B18">
-        <v>2014</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>40.92</v>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
       </c>
       <c r="E18">
-        <v>58.71</v>
+        <v>64.12</v>
       </c>
       <c r="F18">
-        <v>57.25</v>
+        <v>62.1</v>
       </c>
       <c r="G18">
-        <v>39.29</v>
+        <v>46.96</v>
       </c>
       <c r="H18">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="I18">
         <v>9.9</v>
       </c>
       <c r="J18">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1034,23 +1739,23 @@
       <c r="A19">
         <v>49020</v>
       </c>
-      <c r="B19">
-        <v>2014</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>44.83</v>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>30</v>
       </c>
       <c r="E19">
-        <v>70.66</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="F19">
         <v>67.45</v>
       </c>
       <c r="G19">
-        <v>55.48</v>
+        <v>55.47</v>
       </c>
       <c r="H19">
         <v>0.6</v>
@@ -1069,32 +1774,32 @@
       <c r="A20">
         <v>49021</v>
       </c>
-      <c r="B20">
-        <v>2014</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20">
-        <v>39.52</v>
+      <c r="B20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>31</v>
       </c>
       <c r="E20">
-        <v>55.91</v>
+        <v>59.72</v>
       </c>
       <c r="F20">
-        <v>54.65</v>
+        <v>57.79</v>
       </c>
       <c r="G20">
-        <v>37.94</v>
+        <v>41.47</v>
       </c>
       <c r="H20">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="I20">
-        <v>12.3</v>
+        <v>13.0</v>
       </c>
       <c r="J20">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -1104,23 +1809,23 @@
       <c r="A21">
         <v>49001</v>
       </c>
-      <c r="B21">
-        <v>2014</v>
-      </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21">
-        <v>64.52</v>
+      <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s">
+        <v>33</v>
       </c>
       <c r="E21">
-        <v>91.63</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="F21">
         <v>88.76000000000001</v>
       </c>
       <c r="G21">
-        <v>71.77</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="H21">
         <v>0.54</v>
@@ -1139,32 +1844,32 @@
       <c r="A22">
         <v>49002</v>
       </c>
-      <c r="B22">
-        <v>2014</v>
-      </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-      <c r="D22">
-        <v>71.56</v>
+      <c r="B22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s">
+        <v>34</v>
       </c>
       <c r="E22">
-        <v>104.92</v>
+        <v>99.78</v>
       </c>
       <c r="F22">
-        <v>100.87</v>
+        <v>96.27</v>
       </c>
       <c r="G22">
-        <v>87.3</v>
+        <v>81.89</v>
       </c>
       <c r="H22">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="I22">
         <v>11.2</v>
       </c>
       <c r="J22">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1174,23 +1879,23 @@
       <c r="A23">
         <v>49003</v>
       </c>
-      <c r="B23">
-        <v>2014</v>
-      </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
-      <c r="D23">
-        <v>71.060000000000002</v>
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
+        <v>35</v>
       </c>
       <c r="E23">
-        <v>104.65000000000001</v>
+        <v>103.12</v>
       </c>
       <c r="F23">
-        <v>100.78</v>
+        <v>99.63</v>
       </c>
       <c r="G23">
-        <v>89.89</v>
+        <v>86.84</v>
       </c>
       <c r="H23">
         <v>0.46</v>
@@ -1209,23 +1914,23 @@
       <c r="A24">
         <v>49004</v>
       </c>
-      <c r="B24">
-        <v>2014</v>
-      </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
-      <c r="D24">
-        <v>71.56</v>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" t="s">
+        <v>36</v>
       </c>
       <c r="E24">
-        <v>103.31999999999999</v>
+        <v>106.17</v>
       </c>
       <c r="F24">
-        <v>100.31999999999999</v>
+        <v>102.45</v>
       </c>
       <c r="G24">
-        <v>84.73999999999999</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="H24">
         <v>0.47</v>
@@ -1234,7 +1939,7 @@
         <v>12.9</v>
       </c>
       <c r="J24">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1244,23 +1949,23 @@
       <c r="A25">
         <v>49005</v>
       </c>
-      <c r="B25">
-        <v>2014</v>
-      </c>
-      <c r="C25">
-        <v>2</v>
-      </c>
-      <c r="D25">
-        <v>67.78</v>
+      <c r="B25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" t="s">
+        <v>37</v>
       </c>
       <c r="E25">
-        <v>99.97</v>
+        <v>100.25</v>
       </c>
       <c r="F25">
-        <v>96.27</v>
+        <v>96.45</v>
       </c>
       <c r="G25">
-        <v>85.39</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H25">
         <v>0.46</v>
@@ -1269,7 +1974,7 @@
         <v>12.5</v>
       </c>
       <c r="J25">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -1279,23 +1984,23 @@
       <c r="A26">
         <v>49006</v>
       </c>
-      <c r="B26">
-        <v>2014</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>61.99</v>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" t="s">
+        <v>38</v>
       </c>
       <c r="E26">
-        <v>86.55</v>
+        <v>86.019999999999996</v>
       </c>
       <c r="F26">
-        <v>84.23999999999999</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="G26">
-        <v>67.89</v>
+        <v>66.78</v>
       </c>
       <c r="H26">
         <v>0.55</v>
@@ -1314,29 +2019,29 @@
       <c r="A27">
         <v>49007</v>
       </c>
-      <c r="B27">
-        <v>2014</v>
-      </c>
-      <c r="C27">
-        <v>2</v>
-      </c>
-      <c r="D27">
-        <v>68.66</v>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" t="s">
+        <v>39</v>
       </c>
       <c r="E27">
-        <v>100.91</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="F27">
-        <v>97.22</v>
+        <v>96.090000000000003</v>
       </c>
       <c r="G27">
-        <v>83.20999999999999</v>
+        <v>82.19</v>
       </c>
       <c r="H27">
         <v>0.49</v>
       </c>
       <c r="I27">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="J27">
         <v>36</v>
@@ -1349,17 +2054,17 @@
       <c r="A28">
         <v>49008</v>
       </c>
-      <c r="B28">
-        <v>2014</v>
-      </c>
-      <c r="C28">
-        <v>2</v>
-      </c>
-      <c r="D28">
-        <v>63.87</v>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>40</v>
       </c>
       <c r="E28">
-        <v>92.17</v>
+        <v>92.16</v>
       </c>
       <c r="F28">
         <v>88.93000000000001</v>
@@ -1384,26 +2089,26 @@
       <c r="A29">
         <v>49009</v>
       </c>
-      <c r="B29">
-        <v>2014</v>
-      </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-      <c r="D29">
-        <v>64.45999999999999</v>
+      <c r="B29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" t="s">
+        <v>41</v>
       </c>
       <c r="E29">
-        <v>92.95</v>
+        <v>95.36</v>
       </c>
       <c r="F29">
-        <v>89.76000000000001</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="G29">
-        <v>73.93000000000001</v>
+        <v>78.060000000000002</v>
       </c>
       <c r="H29">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="I29">
         <v>10.0</v>
@@ -1419,23 +2124,23 @@
       <c r="A30">
         <v>49010</v>
       </c>
-      <c r="B30">
-        <v>2014</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-      <c r="D30">
-        <v>66.61</v>
+      <c r="B30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" t="s">
+        <v>42</v>
       </c>
       <c r="E30">
-        <v>94.81999999999999</v>
+        <v>94.079999999999998</v>
       </c>
       <c r="F30">
-        <v>92.34</v>
+        <v>91.63</v>
       </c>
       <c r="G30">
-        <v>76.81</v>
+        <v>75.56</v>
       </c>
       <c r="H30">
         <v>0.49</v>
@@ -1454,26 +2159,26 @@
       <c r="A31">
         <v>49011</v>
       </c>
-      <c r="B31">
-        <v>2014</v>
-      </c>
-      <c r="C31">
-        <v>2</v>
-      </c>
-      <c r="D31">
-        <v>63.9</v>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" t="s">
+        <v>43</v>
       </c>
       <c r="E31">
-        <v>88.54000000000001</v>
+        <v>90.34</v>
       </c>
       <c r="F31">
-        <v>86.51000000000001</v>
+        <v>87.89</v>
       </c>
       <c r="G31">
-        <v>66.26000000000001</v>
+        <v>69.56</v>
       </c>
       <c r="H31">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="I31">
         <v>12.1</v>
@@ -1489,23 +2194,23 @@
       <c r="A32">
         <v>49012</v>
       </c>
-      <c r="B32">
-        <v>2014</v>
-      </c>
-      <c r="C32">
-        <v>2</v>
-      </c>
-      <c r="D32">
-        <v>68.53</v>
+      <c r="B32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" t="s">
+        <v>44</v>
       </c>
       <c r="E32">
-        <v>100.17</v>
+        <v>100.18000000000001</v>
       </c>
       <c r="F32">
-        <v>96.52</v>
+        <v>96.53</v>
       </c>
       <c r="G32">
-        <v>84.31999999999999</v>
+        <v>84.33</v>
       </c>
       <c r="H32">
         <v>0.47</v>
@@ -1524,23 +2229,23 @@
       <c r="A33">
         <v>49013</v>
       </c>
-      <c r="B33">
-        <v>2014</v>
-      </c>
-      <c r="C33">
-        <v>2</v>
-      </c>
-      <c r="D33">
-        <v>69.78</v>
+      <c r="B33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" t="s">
+        <v>45</v>
       </c>
       <c r="E33">
-        <v>100.20999999999999</v>
+        <v>101.049999999999997</v>
       </c>
       <c r="F33">
-        <v>97.16</v>
+        <v>97.84</v>
       </c>
       <c r="G33">
-        <v>81.88</v>
+        <v>83.59</v>
       </c>
       <c r="H33">
         <v>0.49</v>
@@ -1559,23 +2264,23 @@
       <c r="A34">
         <v>49014</v>
       </c>
-      <c r="B34">
-        <v>2014</v>
-      </c>
-      <c r="C34">
-        <v>2</v>
-      </c>
-      <c r="D34">
-        <v>68.62</v>
+      <c r="B34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
       </c>
       <c r="E34">
-        <v>98.73999999999999</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="F34">
-        <v>95.65000000000001</v>
+        <v>95.45</v>
       </c>
       <c r="G34">
-        <v>81.5</v>
+        <v>80.87</v>
       </c>
       <c r="H34">
         <v>0.5</v>
@@ -1594,29 +2299,29 @@
       <c r="A35">
         <v>49017</v>
       </c>
-      <c r="B35">
-        <v>2014</v>
-      </c>
-      <c r="C35">
-        <v>2</v>
-      </c>
-      <c r="D35">
-        <v>66.97</v>
+      <c r="B35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" t="s">
+        <v>47</v>
       </c>
       <c r="E35">
-        <v>97.83</v>
+        <v>89.81</v>
       </c>
       <c r="F35">
-        <v>94.31</v>
+        <v>87.14</v>
       </c>
       <c r="G35">
-        <v>79.19</v>
+        <v>68.62</v>
       </c>
       <c r="H35">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="I35">
-        <v>11.5</v>
+        <v>9.9</v>
       </c>
       <c r="J35">
         <v>36</v>
@@ -1629,29 +2334,29 @@
       <c r="A36">
         <v>49018</v>
       </c>
-      <c r="B36">
-        <v>2014</v>
-      </c>
-      <c r="C36">
-        <v>2</v>
-      </c>
-      <c r="D36">
-        <v>69.099999999999994</v>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" t="s">
+        <v>48</v>
       </c>
       <c r="E36">
-        <v>100.79000000000001</v>
+        <v>97.52</v>
       </c>
       <c r="F36">
-        <v>97.28</v>
+        <v>94.22</v>
       </c>
       <c r="G36">
-        <v>84.019999999999996</v>
+        <v>80.66</v>
       </c>
       <c r="H36">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="I36">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="J36">
         <v>36</v>
@@ -1664,32 +2369,32 @@
       <c r="A37">
         <v>49019</v>
       </c>
-      <c r="B37">
-        <v>2014</v>
-      </c>
-      <c r="C37">
-        <v>2</v>
-      </c>
-      <c r="D37">
-        <v>60.84</v>
+      <c r="B37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" t="s">
+        <v>49</v>
       </c>
       <c r="E37">
-        <v>82.11</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="F37">
-        <v>80.54000000000001</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="G37">
-        <v>58.25</v>
+        <v>64.83</v>
       </c>
       <c r="H37">
-        <v>0.56</v>
+        <v>0.54</v>
       </c>
       <c r="I37">
         <v>10.4</v>
       </c>
       <c r="J37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -1699,14 +2404,14 @@
       <c r="A38">
         <v>49020</v>
       </c>
-      <c r="B38">
-        <v>2014</v>
-      </c>
-      <c r="C38">
-        <v>2</v>
-      </c>
-      <c r="D38">
-        <v>69.36</v>
+      <c r="B38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" t="s">
+        <v>50</v>
       </c>
       <c r="E38">
         <v>100.66</v>
@@ -1715,7 +2420,7 @@
         <v>97.17</v>
       </c>
       <c r="G38">
-        <v>82.83</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="H38">
         <v>0.49</v>
@@ -1734,32 +2439,32 @@
       <c r="A39">
         <v>49021</v>
       </c>
-      <c r="B39">
-        <v>2014</v>
-      </c>
-      <c r="C39">
-        <v>2</v>
-      </c>
-      <c r="D39">
-        <v>63.41</v>
+      <c r="B39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" t="s">
+        <v>51</v>
       </c>
       <c r="E39">
-        <v>86.79000000000001</v>
+        <v>97.64</v>
       </c>
       <c r="F39">
-        <v>85.14</v>
+        <v>94.89</v>
       </c>
       <c r="G39">
-        <v>64.67</v>
+        <v>78.66</v>
       </c>
       <c r="H39">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="I39">
-        <v>12.2</v>
+        <v>12.7</v>
       </c>
       <c r="J39">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -1769,23 +2474,23 @@
       <c r="A40">
         <v>49001</v>
       </c>
-      <c r="B40">
-        <v>2014</v>
-      </c>
-      <c r="C40">
-        <v>3</v>
-      </c>
-      <c r="D40">
-        <v>120.45</v>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" t="s">
+        <v>53</v>
       </c>
       <c r="E40">
-        <v>154.31999999999999</v>
+        <v>154.33000000000001</v>
       </c>
       <c r="F40">
-        <v>151.66999999999999</v>
+        <v>151.66</v>
       </c>
       <c r="G40">
-        <v>133.91</v>
+        <v>133.90000000000001</v>
       </c>
       <c r="H40">
         <v>0.42</v>
@@ -1804,32 +2509,32 @@
       <c r="A41">
         <v>49002</v>
       </c>
-      <c r="B41">
-        <v>2014</v>
-      </c>
-      <c r="C41">
-        <v>3</v>
-      </c>
-      <c r="D41">
-        <v>125.8</v>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" t="s">
+        <v>54</v>
       </c>
       <c r="E41">
-        <v>161.15000000000001</v>
+        <v>157.31999999999999</v>
       </c>
       <c r="F41">
-        <v>158.11000000000001</v>
+        <v>154.53</v>
       </c>
       <c r="G41">
-        <v>141.030000000000001</v>
+        <v>138.12</v>
       </c>
       <c r="H41">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="I41">
         <v>11.6</v>
       </c>
       <c r="J41">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -1839,23 +2544,23 @@
       <c r="A42">
         <v>49003</v>
       </c>
-      <c r="B42">
-        <v>2014</v>
-      </c>
-      <c r="C42">
-        <v>3</v>
-      </c>
-      <c r="D42">
-        <v>124.19</v>
+      <c r="B42" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42" t="s">
+        <v>55</v>
       </c>
       <c r="E42">
-        <v>159.81999999999999</v>
+        <v>159.36000000000001</v>
       </c>
       <c r="F42">
-        <v>156.86000000000001</v>
+        <v>156.58000000000001</v>
       </c>
       <c r="G42">
-        <v>139.71000000000001</v>
+        <v>137.97</v>
       </c>
       <c r="H42">
         <v>0.4</v>
@@ -1874,23 +2579,23 @@
       <c r="A43">
         <v>49004</v>
       </c>
-      <c r="B43">
-        <v>2014</v>
-      </c>
-      <c r="C43">
-        <v>3</v>
-      </c>
-      <c r="D43">
-        <v>123.81</v>
+      <c r="B43" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" t="s">
+        <v>56</v>
       </c>
       <c r="E43">
-        <v>158.56999999999999</v>
+        <v>159.15000000000001</v>
       </c>
       <c r="F43">
-        <v>156.13</v>
+        <v>156.33000000000001</v>
       </c>
       <c r="G43">
-        <v>138.58000000000001</v>
+        <v>139.78999999999999</v>
       </c>
       <c r="H43">
         <v>0.4</v>
@@ -1899,7 +2604,7 @@
         <v>13.0</v>
       </c>
       <c r="J43">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -1909,20 +2614,20 @@
       <c r="A44">
         <v>49005</v>
       </c>
-      <c r="B44">
-        <v>2014</v>
-      </c>
-      <c r="C44">
-        <v>3</v>
-      </c>
-      <c r="D44">
-        <v>121.84999999999999</v>
+      <c r="B44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" t="s">
+        <v>57</v>
       </c>
       <c r="E44">
-        <v>157.25</v>
+        <v>157.28999999999999</v>
       </c>
       <c r="F44">
-        <v>154.31</v>
+        <v>154.30000000000001</v>
       </c>
       <c r="G44">
         <v>138.56</v>
@@ -1934,7 +2639,7 @@
         <v>13.0</v>
       </c>
       <c r="J44">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -1944,23 +2649,23 @@
       <c r="A45">
         <v>49006</v>
       </c>
-      <c r="B45">
-        <v>2014</v>
-      </c>
-      <c r="C45">
-        <v>3</v>
-      </c>
-      <c r="D45">
-        <v>118.88</v>
+      <c r="B45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" t="s">
+        <v>58</v>
       </c>
       <c r="E45">
-        <v>150.34999999999999</v>
+        <v>150.090000000000003</v>
       </c>
       <c r="F45">
-        <v>148.16999999999999</v>
+        <v>147.96000000000001</v>
       </c>
       <c r="G45">
-        <v>126.98</v>
+        <v>126.019999999999996</v>
       </c>
       <c r="H45">
         <v>0.44</v>
@@ -1979,29 +2684,29 @@
       <c r="A46">
         <v>49007</v>
       </c>
-      <c r="B46">
-        <v>2014</v>
-      </c>
-      <c r="C46">
-        <v>3</v>
-      </c>
-      <c r="D46">
-        <v>120.45999999999999</v>
+      <c r="B46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" t="s">
+        <v>59</v>
       </c>
       <c r="E46">
-        <v>154.88</v>
+        <v>156.13999999999999</v>
       </c>
       <c r="F46">
-        <v>152.039999999999992</v>
+        <v>153.22</v>
       </c>
       <c r="G46">
-        <v>135.72999999999999</v>
+        <v>137.83000000000001</v>
       </c>
       <c r="H46">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="I46">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="J46">
         <v>36</v>
@@ -2014,23 +2719,23 @@
       <c r="A47">
         <v>49008</v>
       </c>
-      <c r="B47">
-        <v>2014</v>
-      </c>
-      <c r="C47">
-        <v>3</v>
-      </c>
-      <c r="D47">
-        <v>121.47</v>
+      <c r="B47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" t="s">
+        <v>60</v>
       </c>
       <c r="E47">
-        <v>157.25</v>
+        <v>157.24000000000001</v>
       </c>
       <c r="F47">
         <v>154.19</v>
       </c>
       <c r="G47">
-        <v>137.68000000000001</v>
+        <v>137.66999999999999</v>
       </c>
       <c r="H47">
         <v>0.41</v>
@@ -2049,26 +2754,26 @@
       <c r="A48">
         <v>49009</v>
       </c>
-      <c r="B48">
-        <v>2014</v>
-      </c>
-      <c r="C48">
-        <v>3</v>
-      </c>
-      <c r="D48">
-        <v>120.060000000000002</v>
+      <c r="B48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" t="s">
+        <v>52</v>
+      </c>
+      <c r="D48" t="s">
+        <v>61</v>
       </c>
       <c r="E48">
-        <v>154.25999999999999</v>
+        <v>153.43000000000001</v>
       </c>
       <c r="F48">
-        <v>151.44999999999999</v>
+        <v>150.61000000000001</v>
       </c>
       <c r="G48">
-        <v>135.18000000000001</v>
+        <v>136.0</v>
       </c>
       <c r="H48">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="I48">
         <v>11.0</v>
@@ -2084,17 +2789,17 @@
       <c r="A49">
         <v>49010</v>
       </c>
-      <c r="B49">
-        <v>2014</v>
-      </c>
-      <c r="C49">
-        <v>3</v>
-      </c>
-      <c r="D49">
-        <v>121.5</v>
+      <c r="B49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49" t="s">
+        <v>62</v>
       </c>
       <c r="E49">
-        <v>154.13999999999999</v>
+        <v>154.15000000000001</v>
       </c>
       <c r="F49">
         <v>152.039999999999992</v>
@@ -2119,26 +2824,26 @@
       <c r="A50">
         <v>49011</v>
       </c>
-      <c r="B50">
-        <v>2014</v>
-      </c>
-      <c r="C50">
-        <v>3</v>
-      </c>
-      <c r="D50">
-        <v>119.26000000000001</v>
+      <c r="B50" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" t="s">
+        <v>52</v>
+      </c>
+      <c r="D50" t="s">
+        <v>63</v>
       </c>
       <c r="E50">
-        <v>151.25999999999999</v>
+        <v>152.46000000000001</v>
       </c>
       <c r="F50">
-        <v>149.27000000000001</v>
+        <v>150.15000000000001</v>
       </c>
       <c r="G50">
-        <v>126.3</v>
+        <v>129.16</v>
       </c>
       <c r="H50">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="I50">
         <v>12.3</v>
@@ -2154,23 +2859,23 @@
       <c r="A51">
         <v>49012</v>
       </c>
-      <c r="B51">
-        <v>2014</v>
-      </c>
-      <c r="C51">
-        <v>3</v>
-      </c>
-      <c r="D51">
-        <v>121.18000000000001</v>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" t="s">
+        <v>52</v>
+      </c>
+      <c r="D51" t="s">
+        <v>64</v>
       </c>
       <c r="E51">
-        <v>155.78</v>
+        <v>155.80000000000001</v>
       </c>
       <c r="F51">
-        <v>152.88999999999999</v>
+        <v>152.91</v>
       </c>
       <c r="G51">
-        <v>137.050000000000011</v>
+        <v>137.069999999999993</v>
       </c>
       <c r="H51">
         <v>0.4</v>
@@ -2189,23 +2894,23 @@
       <c r="A52">
         <v>49013</v>
       </c>
-      <c r="B52">
-        <v>2014</v>
-      </c>
-      <c r="C52">
-        <v>3</v>
-      </c>
-      <c r="D52">
-        <v>123.51000000000001</v>
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" t="s">
+        <v>52</v>
+      </c>
+      <c r="D52" t="s">
+        <v>65</v>
       </c>
       <c r="E52">
-        <v>157.65000000000001</v>
+        <v>158.15000000000001</v>
       </c>
       <c r="F52">
-        <v>155.15000000000001</v>
+        <v>155.56999999999999</v>
       </c>
       <c r="G52">
-        <v>132.93000000000001</v>
+        <v>136.090000000000003</v>
       </c>
       <c r="H52">
         <v>0.41</v>
@@ -2224,23 +2929,23 @@
       <c r="A53">
         <v>49014</v>
       </c>
-      <c r="B53">
-        <v>2014</v>
-      </c>
-      <c r="C53">
-        <v>3</v>
-      </c>
-      <c r="D53">
-        <v>122.65000000000001</v>
+      <c r="B53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" t="s">
+        <v>66</v>
       </c>
       <c r="E53">
-        <v>157.090000000000003</v>
+        <v>157.12</v>
       </c>
       <c r="F53">
-        <v>154.5</v>
+        <v>154.47999999999999</v>
       </c>
       <c r="G53">
-        <v>137.19</v>
+        <v>136.62</v>
       </c>
       <c r="H53">
         <v>0.41</v>
@@ -2259,29 +2964,29 @@
       <c r="A54">
         <v>49017</v>
       </c>
-      <c r="B54">
-        <v>2014</v>
-      </c>
-      <c r="C54">
-        <v>3</v>
-      </c>
-      <c r="D54">
-        <v>119.75</v>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" t="s">
+        <v>52</v>
+      </c>
+      <c r="D54" t="s">
+        <v>67</v>
       </c>
       <c r="E54">
-        <v>153.63</v>
+        <v>152.91999999999999</v>
       </c>
       <c r="F54">
-        <v>150.84</v>
+        <v>150.38</v>
       </c>
       <c r="G54">
-        <v>134.84</v>
+        <v>132.18000000000001</v>
       </c>
       <c r="H54">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="I54">
-        <v>12.0</v>
+        <v>10.7</v>
       </c>
       <c r="J54">
         <v>36</v>
@@ -2294,29 +2999,29 @@
       <c r="A55">
         <v>49018</v>
       </c>
-      <c r="B55">
-        <v>2014</v>
-      </c>
-      <c r="C55">
-        <v>3</v>
-      </c>
-      <c r="D55">
-        <v>118.81999999999999</v>
+      <c r="B55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" t="s">
+        <v>52</v>
+      </c>
+      <c r="D55" t="s">
+        <v>68</v>
       </c>
       <c r="E55">
-        <v>151.94999999999999</v>
+        <v>153.91999999999999</v>
       </c>
       <c r="F55">
-        <v>149.33000000000001</v>
+        <v>151.25999999999999</v>
       </c>
       <c r="G55">
-        <v>133.02000000000001</v>
+        <v>134.88999999999999</v>
       </c>
       <c r="H55">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="I55">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="J55">
         <v>36</v>
@@ -2329,32 +3034,32 @@
       <c r="A56">
         <v>49019</v>
       </c>
-      <c r="B56">
-        <v>2014</v>
-      </c>
-      <c r="C56">
-        <v>3</v>
-      </c>
-      <c r="D56">
-        <v>115.89</v>
+      <c r="B56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" t="s">
+        <v>52</v>
+      </c>
+      <c r="D56" t="s">
+        <v>69</v>
       </c>
       <c r="E56">
-        <v>144.88</v>
+        <v>147.18000000000001</v>
       </c>
       <c r="F56">
-        <v>143.27000000000001</v>
+        <v>145.31999999999999</v>
       </c>
       <c r="G56">
-        <v>112.38</v>
+        <v>116.86</v>
       </c>
       <c r="H56">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I56">
         <v>11.0</v>
       </c>
       <c r="J56">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -2364,23 +3069,23 @@
       <c r="A57">
         <v>49020</v>
       </c>
-      <c r="B57">
-        <v>2014</v>
-      </c>
-      <c r="C57">
-        <v>3</v>
-      </c>
-      <c r="D57">
-        <v>122.010000000000005</v>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>52</v>
+      </c>
+      <c r="D57" t="s">
+        <v>70</v>
       </c>
       <c r="E57">
-        <v>155.19999999999999</v>
+        <v>155.13999999999999</v>
       </c>
       <c r="F57">
-        <v>152.56999999999999</v>
+        <v>152.52000000000001</v>
       </c>
       <c r="G57">
-        <v>133.59</v>
+        <v>132.71000000000001</v>
       </c>
       <c r="H57">
         <v>0.43</v>
@@ -2399,32 +3104,32 @@
       <c r="A58">
         <v>49021</v>
       </c>
-      <c r="B58">
-        <v>2014</v>
-      </c>
-      <c r="C58">
-        <v>3</v>
-      </c>
-      <c r="D58">
-        <v>116.010000000000005</v>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" t="s">
+        <v>52</v>
+      </c>
+      <c r="D58" t="s">
+        <v>71</v>
       </c>
       <c r="E58">
-        <v>145.80000000000001</v>
+        <v>155.0</v>
       </c>
       <c r="F58">
-        <v>144.21000000000001</v>
+        <v>152.62</v>
       </c>
       <c r="G58">
-        <v>115.29000000000001</v>
+        <v>132.97999999999999</v>
       </c>
       <c r="H58">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="I58">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="J58">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K58">
         <v>0</v>
@@ -2434,23 +3139,23 @@
       <c r="A59">
         <v>49001</v>
       </c>
-      <c r="B59">
-        <v>2014</v>
-      </c>
-      <c r="C59">
-        <v>4</v>
-      </c>
-      <c r="D59">
-        <v>142.27000000000001</v>
+      <c r="B59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" t="s">
+        <v>72</v>
+      </c>
+      <c r="D59" t="s">
+        <v>73</v>
       </c>
       <c r="E59">
-        <v>153.30000000000001</v>
+        <v>153.28999999999999</v>
       </c>
       <c r="F59">
         <v>154.28999999999999</v>
       </c>
       <c r="G59">
-        <v>120.030000000000001</v>
+        <v>120.23</v>
       </c>
       <c r="H59">
         <v>0.5</v>
@@ -2469,32 +3174,32 @@
       <c r="A60">
         <v>49002</v>
       </c>
-      <c r="B60">
-        <v>2014</v>
-      </c>
-      <c r="C60">
-        <v>4</v>
-      </c>
-      <c r="D60">
-        <v>161.61000000000001</v>
+      <c r="B60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" t="s">
+        <v>72</v>
+      </c>
+      <c r="D60" t="s">
+        <v>74</v>
       </c>
       <c r="E60">
-        <v>177.59999999999999</v>
+        <v>172.59999999999999</v>
       </c>
       <c r="F60">
-        <v>178.65000000000001</v>
+        <v>173.58000000000001</v>
       </c>
       <c r="G60">
-        <v>157.16999999999999</v>
+        <v>151.99000000000001</v>
       </c>
       <c r="H60">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="I60">
         <v>14.4</v>
       </c>
       <c r="J60">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K60">
         <v>0</v>
@@ -2504,23 +3209,23 @@
       <c r="A61">
         <v>49003</v>
       </c>
-      <c r="B61">
-        <v>2014</v>
-      </c>
-      <c r="C61">
-        <v>4</v>
-      </c>
-      <c r="D61">
-        <v>162.37</v>
+      <c r="B61" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" t="s">
+        <v>72</v>
+      </c>
+      <c r="D61" t="s">
+        <v>75</v>
       </c>
       <c r="E61">
-        <v>178.55000000000001</v>
+        <v>178.63999999999999</v>
       </c>
       <c r="F61">
-        <v>179.50999999999999</v>
+        <v>179.47999999999999</v>
       </c>
       <c r="G61">
-        <v>159.0099999999999909</v>
+        <v>158.63</v>
       </c>
       <c r="H61">
         <v>0.39</v>
@@ -2539,23 +3244,23 @@
       <c r="A62">
         <v>49004</v>
       </c>
-      <c r="B62">
-        <v>2014</v>
-      </c>
-      <c r="C62">
-        <v>4</v>
-      </c>
-      <c r="D62">
-        <v>164.47999999999999</v>
+      <c r="B62" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" t="s">
+        <v>72</v>
+      </c>
+      <c r="D62" t="s">
+        <v>76</v>
       </c>
       <c r="E62">
-        <v>181.36000000000001</v>
+        <v>181.12</v>
       </c>
       <c r="F62">
-        <v>181.97999999999999</v>
+        <v>181.99000000000001</v>
       </c>
       <c r="G62">
-        <v>162.50999999999999</v>
+        <v>162.96000000000001</v>
       </c>
       <c r="H62">
         <v>0.38</v>
@@ -2564,7 +3269,7 @@
         <v>15.1</v>
       </c>
       <c r="J62">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -2574,23 +3279,23 @@
       <c r="A63">
         <v>49005</v>
       </c>
-      <c r="B63">
-        <v>2014</v>
-      </c>
-      <c r="C63">
-        <v>4</v>
-      </c>
-      <c r="D63">
-        <v>159.22</v>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
+        <v>72</v>
+      </c>
+      <c r="D63" t="s">
+        <v>77</v>
       </c>
       <c r="E63">
-        <v>174.93000000000001</v>
+        <v>174.90000000000001</v>
       </c>
       <c r="F63">
-        <v>175.84999999999999</v>
+        <v>175.86000000000001</v>
       </c>
       <c r="G63">
-        <v>153.25999999999999</v>
+        <v>153.16</v>
       </c>
       <c r="H63">
         <v>0.4</v>
@@ -2599,7 +3304,7 @@
         <v>14.9</v>
       </c>
       <c r="J63">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -2609,23 +3314,23 @@
       <c r="A64">
         <v>49006</v>
       </c>
-      <c r="B64">
-        <v>2014</v>
-      </c>
-      <c r="C64">
-        <v>4</v>
-      </c>
-      <c r="D64">
-        <v>145.75</v>
+      <c r="B64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" t="s">
+        <v>72</v>
+      </c>
+      <c r="D64" t="s">
+        <v>78</v>
       </c>
       <c r="E64">
-        <v>157.63999999999999</v>
+        <v>157.66</v>
       </c>
       <c r="F64">
         <v>158.47999999999999</v>
       </c>
       <c r="G64">
-        <v>129.02000000000001</v>
+        <v>129.86000000000001</v>
       </c>
       <c r="H64">
         <v>0.47</v>
@@ -2644,29 +3349,29 @@
       <c r="A65">
         <v>49007</v>
       </c>
-      <c r="B65">
-        <v>2014</v>
-      </c>
-      <c r="C65">
-        <v>4</v>
-      </c>
-      <c r="D65">
-        <v>148.31</v>
+      <c r="B65" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" t="s">
+        <v>72</v>
+      </c>
+      <c r="D65" t="s">
+        <v>79</v>
       </c>
       <c r="E65">
-        <v>161.44999999999999</v>
+        <v>159.94</v>
       </c>
       <c r="F65">
-        <v>162.41</v>
+        <v>160.96000000000001</v>
       </c>
       <c r="G65">
-        <v>132.52000000000001</v>
+        <v>130.87</v>
       </c>
       <c r="H65">
         <v>0.46</v>
       </c>
       <c r="I65">
-        <v>13.9</v>
+        <v>14.0</v>
       </c>
       <c r="J65">
         <v>36</v>
@@ -2679,14 +3384,14 @@
       <c r="A66">
         <v>49008</v>
       </c>
-      <c r="B66">
-        <v>2014</v>
-      </c>
-      <c r="C66">
-        <v>4</v>
-      </c>
-      <c r="D66">
-        <v>143.5</v>
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>72</v>
+      </c>
+      <c r="D66" t="s">
+        <v>80</v>
       </c>
       <c r="E66">
         <v>156.22999999999999</v>
@@ -2714,26 +3419,26 @@
       <c r="A67">
         <v>49009</v>
       </c>
-      <c r="B67">
-        <v>2014</v>
-      </c>
-      <c r="C67">
-        <v>4</v>
-      </c>
-      <c r="D67">
-        <v>143.38999999999999</v>
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" t="s">
+        <v>72</v>
+      </c>
+      <c r="D67" t="s">
+        <v>81</v>
       </c>
       <c r="E67">
-        <v>155.74000000000001</v>
+        <v>160.13999999999999</v>
       </c>
       <c r="F67">
-        <v>156.66999999999999</v>
+        <v>160.96000000000001</v>
       </c>
       <c r="G67">
-        <v>123.89</v>
+        <v>132.65000000000001</v>
       </c>
       <c r="H67">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="I67">
         <v>13.7</v>
@@ -2749,26 +3454,26 @@
       <c r="A68">
         <v>49010</v>
       </c>
-      <c r="B68">
-        <v>2014</v>
-      </c>
-      <c r="C68">
-        <v>4</v>
-      </c>
-      <c r="D68">
-        <v>157.080000000000013</v>
+      <c r="B68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" t="s">
+        <v>72</v>
+      </c>
+      <c r="D68" t="s">
+        <v>82</v>
       </c>
       <c r="E68">
-        <v>172.69</v>
+        <v>171.63999999999999</v>
       </c>
       <c r="F68">
-        <v>173.22</v>
+        <v>172.18000000000001</v>
       </c>
       <c r="G68">
-        <v>139.65000000000001</v>
+        <v>136.65000000000001</v>
       </c>
       <c r="H68">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="I68">
         <v>15.1</v>
@@ -2784,23 +3489,23 @@
       <c r="A69">
         <v>49011</v>
       </c>
-      <c r="B69">
-        <v>2014</v>
-      </c>
-      <c r="C69">
-        <v>4</v>
-      </c>
-      <c r="D69">
-        <v>150.59</v>
+      <c r="B69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" t="s">
+        <v>72</v>
+      </c>
+      <c r="D69" t="s">
+        <v>83</v>
       </c>
       <c r="E69">
-        <v>163.81999999999999</v>
+        <v>163.80000000000001</v>
       </c>
       <c r="F69">
-        <v>164.47999999999999</v>
+        <v>164.66999999999999</v>
       </c>
       <c r="G69">
-        <v>135.97999999999999</v>
+        <v>137.44999999999999</v>
       </c>
       <c r="H69">
         <v>0.44</v>
@@ -2819,23 +3524,23 @@
       <c r="A70">
         <v>49012</v>
       </c>
-      <c r="B70">
-        <v>2014</v>
-      </c>
-      <c r="C70">
-        <v>4</v>
-      </c>
-      <c r="D70">
-        <v>159.25999999999999</v>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" t="s">
+        <v>72</v>
+      </c>
+      <c r="D70" t="s">
+        <v>84</v>
       </c>
       <c r="E70">
-        <v>175.30000000000001</v>
+        <v>175.31</v>
       </c>
       <c r="F70">
-        <v>176.22</v>
+        <v>176.22999999999999</v>
       </c>
       <c r="G70">
-        <v>154.31999999999999</v>
+        <v>154.52000000000001</v>
       </c>
       <c r="H70">
         <v>0.4</v>
@@ -2854,23 +3559,23 @@
       <c r="A71">
         <v>49013</v>
       </c>
-      <c r="B71">
-        <v>2014</v>
-      </c>
-      <c r="C71">
-        <v>4</v>
-      </c>
-      <c r="D71">
-        <v>163.66</v>
+      <c r="B71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" t="s">
+        <v>72</v>
+      </c>
+      <c r="D71" t="s">
+        <v>85</v>
       </c>
       <c r="E71">
-        <v>179.91999999999999</v>
+        <v>179.94</v>
       </c>
       <c r="F71">
-        <v>180.66999999999999</v>
+        <v>180.75999999999999</v>
       </c>
       <c r="G71">
-        <v>154.75999999999999</v>
+        <v>157.38999999999999</v>
       </c>
       <c r="H71">
         <v>0.4</v>
@@ -2889,23 +3594,23 @@
       <c r="A72">
         <v>49014</v>
       </c>
-      <c r="B72">
-        <v>2014</v>
-      </c>
-      <c r="C72">
-        <v>4</v>
-      </c>
-      <c r="D72">
-        <v>157.65000000000001</v>
+      <c r="B72" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>72</v>
+      </c>
+      <c r="D72" t="s">
+        <v>86</v>
       </c>
       <c r="E72">
-        <v>171.59</v>
+        <v>171.53</v>
       </c>
       <c r="F72">
-        <v>172.49000000000001</v>
+        <v>172.47</v>
       </c>
       <c r="G72">
-        <v>144.52000000000001</v>
+        <v>144.41</v>
       </c>
       <c r="H72">
         <v>0.44</v>
@@ -2924,29 +3629,29 @@
       <c r="A73">
         <v>49017</v>
       </c>
-      <c r="B73">
-        <v>2014</v>
-      </c>
-      <c r="C73">
-        <v>4</v>
-      </c>
-      <c r="D73">
-        <v>147.5</v>
+      <c r="B73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" t="s">
+        <v>72</v>
+      </c>
+      <c r="D73" t="s">
+        <v>87</v>
       </c>
       <c r="E73">
-        <v>160.84</v>
+        <v>155.069999999999993</v>
       </c>
       <c r="F73">
-        <v>161.75999999999999</v>
+        <v>155.93000000000001</v>
       </c>
       <c r="G73">
-        <v>131.87</v>
+        <v>122.010000000000005</v>
       </c>
       <c r="H73">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="I73">
-        <v>14.3</v>
+        <v>13.5</v>
       </c>
       <c r="J73">
         <v>36</v>
@@ -2959,29 +3664,29 @@
       <c r="A74">
         <v>49018</v>
       </c>
-      <c r="B74">
-        <v>2014</v>
-      </c>
-      <c r="C74">
-        <v>4</v>
-      </c>
-      <c r="D74">
-        <v>152.19</v>
+      <c r="B74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" t="s">
+        <v>72</v>
+      </c>
+      <c r="D74" t="s">
+        <v>88</v>
       </c>
       <c r="E74">
-        <v>166.31</v>
+        <v>168.33000000000001</v>
       </c>
       <c r="F74">
-        <v>167.22</v>
+        <v>169.16999999999999</v>
       </c>
       <c r="G74">
-        <v>141.02000000000001</v>
+        <v>145.31</v>
       </c>
       <c r="H74">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="I74">
-        <v>14.3</v>
+        <v>14.7</v>
       </c>
       <c r="J74">
         <v>36</v>
@@ -2994,32 +3699,32 @@
       <c r="A75">
         <v>49019</v>
       </c>
-      <c r="B75">
-        <v>2014</v>
-      </c>
-      <c r="C75">
-        <v>4</v>
-      </c>
-      <c r="D75">
-        <v>144.66999999999999</v>
+      <c r="B75" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" t="s">
+        <v>72</v>
+      </c>
+      <c r="D75" t="s">
+        <v>89</v>
       </c>
       <c r="E75">
-        <v>158.16999999999999</v>
+        <v>161.25999999999999</v>
       </c>
       <c r="F75">
-        <v>158.62</v>
+        <v>161.84</v>
       </c>
       <c r="G75">
-        <v>119.26000000000001</v>
+        <v>128.86000000000001</v>
       </c>
       <c r="H75">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="I75">
         <v>13.7</v>
       </c>
       <c r="J75">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K75">
         <v>0</v>
@@ -3029,14 +3734,14 @@
       <c r="A76">
         <v>49020</v>
       </c>
-      <c r="B76">
-        <v>2014</v>
-      </c>
-      <c r="C76">
-        <v>4</v>
-      </c>
-      <c r="D76">
-        <v>152.88999999999999</v>
+      <c r="B76" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" t="s">
+        <v>72</v>
+      </c>
+      <c r="D76" t="s">
+        <v>90</v>
       </c>
       <c r="E76">
         <v>166.44999999999999</v>
@@ -3045,7 +3750,7 @@
         <v>167.44</v>
       </c>
       <c r="G76">
-        <v>141.91</v>
+        <v>141.90000000000001</v>
       </c>
       <c r="H76">
         <v>0.44</v>
@@ -3064,32 +3769,32 @@
       <c r="A77">
         <v>49021</v>
       </c>
-      <c r="B77">
-        <v>2014</v>
-      </c>
-      <c r="C77">
-        <v>4</v>
-      </c>
-      <c r="D77">
-        <v>157.099999999999994</v>
+      <c r="B77" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" t="s">
+        <v>72</v>
+      </c>
+      <c r="D77" t="s">
+        <v>91</v>
       </c>
       <c r="E77">
-        <v>173.039999999999992</v>
+        <v>177.84</v>
       </c>
       <c r="F77">
-        <v>173.38999999999999</v>
+        <v>178.47999999999999</v>
       </c>
       <c r="G77">
-        <v>139.41</v>
+        <v>156.19999999999999</v>
       </c>
       <c r="H77">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="I77">
-        <v>14.8</v>
+        <v>15.0</v>
       </c>
       <c r="J77">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K77">
         <v>0</v>
@@ -3099,23 +3804,23 @@
       <c r="A78">
         <v>49001</v>
       </c>
-      <c r="B78">
-        <v>2014</v>
-      </c>
-      <c r="C78">
-        <v>5</v>
-      </c>
-      <c r="D78">
-        <v>192.12</v>
+      <c r="B78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" t="s">
+        <v>92</v>
+      </c>
+      <c r="D78" t="s">
+        <v>93</v>
       </c>
       <c r="E78">
-        <v>189.62</v>
+        <v>189.56999999999999</v>
       </c>
       <c r="F78">
-        <v>193.84999999999999</v>
+        <v>193.84</v>
       </c>
       <c r="G78">
-        <v>173.65000000000001</v>
+        <v>174.0</v>
       </c>
       <c r="H78">
         <v>0.39</v>
@@ -3134,32 +3839,32 @@
       <c r="A79">
         <v>49002</v>
       </c>
-      <c r="B79">
-        <v>2014</v>
-      </c>
-      <c r="C79">
-        <v>5</v>
-      </c>
-      <c r="D79">
-        <v>201.30000000000001</v>
+      <c r="B79" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" t="s">
+        <v>92</v>
+      </c>
+      <c r="D79" t="s">
+        <v>94</v>
       </c>
       <c r="E79">
-        <v>196.46000000000001</v>
+        <v>193.84</v>
       </c>
       <c r="F79">
-        <v>202.099999999999994</v>
+        <v>198.90000000000001</v>
       </c>
       <c r="G79">
-        <v>190.44</v>
+        <v>186.060000000000002</v>
       </c>
       <c r="H79">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="I79">
         <v>17.0</v>
       </c>
       <c r="J79">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K79">
         <v>0</v>
@@ -3169,20 +3874,20 @@
       <c r="A80">
         <v>49003</v>
       </c>
-      <c r="B80">
-        <v>2014</v>
-      </c>
-      <c r="C80">
-        <v>5</v>
-      </c>
-      <c r="D80">
-        <v>201.90000000000001</v>
+      <c r="B80" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" t="s">
+        <v>92</v>
+      </c>
+      <c r="D80" t="s">
+        <v>95</v>
       </c>
       <c r="E80">
-        <v>199.080000000000013</v>
+        <v>199.47999999999999</v>
       </c>
       <c r="F80">
-        <v>204.099999999999994</v>
+        <v>204.090000000000003</v>
       </c>
       <c r="G80">
         <v>190.96000000000001</v>
@@ -3204,23 +3909,23 @@
       <c r="A81">
         <v>49004</v>
       </c>
-      <c r="B81">
-        <v>2014</v>
-      </c>
-      <c r="C81">
-        <v>5</v>
-      </c>
-      <c r="D81">
-        <v>200.72</v>
+      <c r="B81" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" t="s">
+        <v>92</v>
+      </c>
+      <c r="D81" t="s">
+        <v>96</v>
       </c>
       <c r="E81">
-        <v>199.25</v>
+        <v>198.40000000000001</v>
       </c>
       <c r="F81">
-        <v>202.99000000000001</v>
+        <v>203.0</v>
       </c>
       <c r="G81">
-        <v>189.50999999999999</v>
+        <v>190.13</v>
       </c>
       <c r="H81">
         <v>0.35</v>
@@ -3229,7 +3934,7 @@
         <v>17.4</v>
       </c>
       <c r="J81">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K81">
         <v>0</v>
@@ -3239,17 +3944,17 @@
       <c r="A82">
         <v>49005</v>
       </c>
-      <c r="B82">
-        <v>2014</v>
-      </c>
-      <c r="C82">
-        <v>5</v>
-      </c>
-      <c r="D82">
-        <v>202.0</v>
+      <c r="B82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" t="s">
+        <v>92</v>
+      </c>
+      <c r="D82" t="s">
+        <v>97</v>
       </c>
       <c r="E82">
-        <v>199.15000000000001</v>
+        <v>199.02000000000001</v>
       </c>
       <c r="F82">
         <v>204.11000000000001</v>
@@ -3264,7 +3969,7 @@
         <v>17.3</v>
       </c>
       <c r="J82">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K82">
         <v>0</v>
@@ -3274,23 +3979,23 @@
       <c r="A83">
         <v>49006</v>
       </c>
-      <c r="B83">
-        <v>2014</v>
-      </c>
-      <c r="C83">
-        <v>5</v>
-      </c>
-      <c r="D83">
-        <v>192.25</v>
+      <c r="B83" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" t="s">
+        <v>92</v>
+      </c>
+      <c r="D83" t="s">
+        <v>98</v>
       </c>
       <c r="E83">
-        <v>189.38</v>
+        <v>189.46000000000001</v>
       </c>
       <c r="F83">
         <v>193.16</v>
       </c>
       <c r="G83">
-        <v>175.30000000000001</v>
+        <v>173.28</v>
       </c>
       <c r="H83">
         <v>0.39</v>
@@ -3309,26 +4014,26 @@
       <c r="A84">
         <v>49007</v>
       </c>
-      <c r="B84">
-        <v>2014</v>
-      </c>
-      <c r="C84">
-        <v>5</v>
-      </c>
-      <c r="D84">
-        <v>197.59999999999999</v>
+      <c r="B84" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" t="s">
+        <v>92</v>
+      </c>
+      <c r="D84" t="s">
+        <v>99</v>
       </c>
       <c r="E84">
-        <v>194.91999999999999</v>
+        <v>193.069999999999993</v>
       </c>
       <c r="F84">
-        <v>199.61000000000001</v>
+        <v>197.78999999999999</v>
       </c>
       <c r="G84">
-        <v>181.78</v>
+        <v>183.31</v>
       </c>
       <c r="H84">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="I84">
         <v>16.6</v>
@@ -3344,14 +4049,14 @@
       <c r="A85">
         <v>49008</v>
       </c>
-      <c r="B85">
-        <v>2014</v>
-      </c>
-      <c r="C85">
-        <v>5</v>
-      </c>
-      <c r="D85">
-        <v>195.11000000000001</v>
+      <c r="B85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" t="s">
+        <v>92</v>
+      </c>
+      <c r="D85" t="s">
+        <v>100</v>
       </c>
       <c r="E85">
         <v>192.44</v>
@@ -3379,26 +4084,26 @@
       <c r="A86">
         <v>49009</v>
       </c>
-      <c r="B86">
-        <v>2014</v>
-      </c>
-      <c r="C86">
-        <v>5</v>
-      </c>
-      <c r="D86">
-        <v>194.30000000000001</v>
+      <c r="B86" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" t="s">
+        <v>92</v>
+      </c>
+      <c r="D86" t="s">
+        <v>101</v>
       </c>
       <c r="E86">
-        <v>191.53999999999999</v>
+        <v>191.71000000000001</v>
       </c>
       <c r="F86">
-        <v>196.030000000000001</v>
+        <v>196.22</v>
       </c>
       <c r="G86">
-        <v>171.84999999999999</v>
+        <v>175.47999999999999</v>
       </c>
       <c r="H86">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="I86">
         <v>16.5</v>
@@ -3414,26 +4119,26 @@
       <c r="A87">
         <v>49010</v>
       </c>
-      <c r="B87">
-        <v>2014</v>
-      </c>
-      <c r="C87">
-        <v>5</v>
-      </c>
-      <c r="D87">
-        <v>196.86000000000001</v>
+      <c r="B87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>92</v>
+      </c>
+      <c r="D87" t="s">
+        <v>102</v>
       </c>
       <c r="E87">
-        <v>196.56</v>
+        <v>196.44</v>
       </c>
       <c r="F87">
-        <v>199.78</v>
+        <v>199.66999999999999</v>
       </c>
       <c r="G87">
-        <v>172.44</v>
+        <v>171.27000000000001</v>
       </c>
       <c r="H87">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="I87">
         <v>17.4</v>
@@ -3449,23 +4154,23 @@
       <c r="A88">
         <v>49011</v>
       </c>
-      <c r="B88">
-        <v>2014</v>
-      </c>
-      <c r="C88">
-        <v>5</v>
-      </c>
-      <c r="D88">
-        <v>193.81999999999999</v>
+      <c r="B88" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" t="s">
+        <v>92</v>
+      </c>
+      <c r="D88" t="s">
+        <v>103</v>
       </c>
       <c r="E88">
-        <v>192.88</v>
+        <v>192.21000000000001</v>
       </c>
       <c r="F88">
-        <v>195.99000000000001</v>
+        <v>196.030000000000001</v>
       </c>
       <c r="G88">
-        <v>173.87</v>
+        <v>175.59</v>
       </c>
       <c r="H88">
         <v>0.38</v>
@@ -3484,23 +4189,23 @@
       <c r="A89">
         <v>49012</v>
       </c>
-      <c r="B89">
-        <v>2014</v>
-      </c>
-      <c r="C89">
-        <v>5</v>
-      </c>
-      <c r="D89">
-        <v>197.13999999999999</v>
+      <c r="B89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" t="s">
+        <v>92</v>
+      </c>
+      <c r="D89" t="s">
+        <v>104</v>
       </c>
       <c r="E89">
         <v>193.56999999999999</v>
       </c>
       <c r="F89">
-        <v>198.56999999999999</v>
+        <v>198.58000000000001</v>
       </c>
       <c r="G89">
-        <v>183.28</v>
+        <v>184.0</v>
       </c>
       <c r="H89">
         <v>0.37</v>
@@ -3519,23 +4224,23 @@
       <c r="A90">
         <v>49013</v>
       </c>
-      <c r="B90">
-        <v>2014</v>
-      </c>
-      <c r="C90">
-        <v>5</v>
-      </c>
-      <c r="D90">
-        <v>200.0099999999999909</v>
+      <c r="B90" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" t="s">
+        <v>92</v>
+      </c>
+      <c r="D90" t="s">
+        <v>105</v>
       </c>
       <c r="E90">
-        <v>198.81999999999999</v>
+        <v>198.69999999999999</v>
       </c>
       <c r="F90">
-        <v>202.78999999999999</v>
+        <v>202.91</v>
       </c>
       <c r="G90">
-        <v>179.41</v>
+        <v>183.50999999999999</v>
       </c>
       <c r="H90">
         <v>0.37</v>
@@ -3554,23 +4259,23 @@
       <c r="A91">
         <v>49014</v>
       </c>
-      <c r="B91">
-        <v>2014</v>
-      </c>
-      <c r="C91">
-        <v>5</v>
-      </c>
-      <c r="D91">
-        <v>196.72999999999999</v>
+      <c r="B91" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" t="s">
+        <v>92</v>
+      </c>
+      <c r="D91" t="s">
+        <v>106</v>
       </c>
       <c r="E91">
-        <v>194.75999999999999</v>
+        <v>194.66</v>
       </c>
       <c r="F91">
         <v>198.84</v>
       </c>
       <c r="G91">
-        <v>177.94999999999999</v>
+        <v>178.72999999999999</v>
       </c>
       <c r="H91">
         <v>0.38</v>
@@ -3589,29 +4294,29 @@
       <c r="A92">
         <v>49017</v>
       </c>
-      <c r="B92">
-        <v>2014</v>
-      </c>
-      <c r="C92">
-        <v>5</v>
-      </c>
-      <c r="D92">
-        <v>197.56999999999999</v>
+      <c r="B92" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" t="s">
+        <v>92</v>
+      </c>
+      <c r="D92" t="s">
+        <v>107</v>
       </c>
       <c r="E92">
-        <v>194.83000000000001</v>
+        <v>193.47</v>
       </c>
       <c r="F92">
-        <v>199.50999999999999</v>
+        <v>197.50999999999999</v>
       </c>
       <c r="G92">
-        <v>179.88999999999999</v>
+        <v>172.80000000000001</v>
       </c>
       <c r="H92">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="I92">
-        <v>17.0</v>
+        <v>16.4</v>
       </c>
       <c r="J92">
         <v>36</v>
@@ -3624,29 +4329,29 @@
       <c r="A93">
         <v>49018</v>
       </c>
-      <c r="B93">
-        <v>2014</v>
-      </c>
-      <c r="C93">
-        <v>5</v>
-      </c>
-      <c r="D93">
-        <v>195.19999999999999</v>
+      <c r="B93" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" t="s">
+        <v>92</v>
+      </c>
+      <c r="D93" t="s">
+        <v>108</v>
       </c>
       <c r="E93">
-        <v>191.43000000000001</v>
+        <v>191.30000000000001</v>
       </c>
       <c r="F93">
-        <v>196.15000000000001</v>
+        <v>196.060000000000002</v>
       </c>
       <c r="G93">
-        <v>183.30000000000001</v>
+        <v>184.050000000000011</v>
       </c>
       <c r="H93">
         <v>0.37</v>
       </c>
       <c r="I93">
-        <v>16.9</v>
+        <v>17.3</v>
       </c>
       <c r="J93">
         <v>36</v>
@@ -3659,23 +4364,23 @@
       <c r="A94">
         <v>49019</v>
       </c>
-      <c r="B94">
-        <v>2014</v>
-      </c>
-      <c r="C94">
-        <v>5</v>
-      </c>
-      <c r="D94">
-        <v>190.71000000000001</v>
+      <c r="B94" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" t="s">
+        <v>92</v>
+      </c>
+      <c r="D94" t="s">
+        <v>109</v>
       </c>
       <c r="E94">
-        <v>189.97999999999999</v>
+        <v>189.75999999999999</v>
       </c>
       <c r="F94">
-        <v>192.72999999999999</v>
+        <v>192.94</v>
       </c>
       <c r="G94">
-        <v>168.19</v>
+        <v>169.94999999999999</v>
       </c>
       <c r="H94">
         <v>0.39</v>
@@ -3684,7 +4389,7 @@
         <v>16.2</v>
       </c>
       <c r="J94">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K94">
         <v>0</v>
@@ -3694,14 +4399,14 @@
       <c r="A95">
         <v>49020</v>
       </c>
-      <c r="B95">
-        <v>2014</v>
-      </c>
-      <c r="C95">
-        <v>5</v>
-      </c>
-      <c r="D95">
-        <v>195.78999999999999</v>
+      <c r="B95" t="s">
+        <v>11</v>
+      </c>
+      <c r="C95" t="s">
+        <v>92</v>
+      </c>
+      <c r="D95" t="s">
+        <v>110</v>
       </c>
       <c r="E95">
         <v>191.66</v>
@@ -3729,32 +4434,32 @@
       <c r="A96">
         <v>49021</v>
       </c>
-      <c r="B96">
-        <v>2014</v>
-      </c>
-      <c r="C96">
-        <v>5</v>
-      </c>
-      <c r="D96">
-        <v>195.050000000000011</v>
+      <c r="B96" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" t="s">
+        <v>92</v>
+      </c>
+      <c r="D96" t="s">
+        <v>111</v>
       </c>
       <c r="E96">
-        <v>195.59999999999999</v>
+        <v>198.11000000000001</v>
       </c>
       <c r="F96">
-        <v>198.099999999999994</v>
+        <v>201.94</v>
       </c>
       <c r="G96">
-        <v>171.02000000000001</v>
+        <v>186.43000000000001</v>
       </c>
       <c r="H96">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="I96">
         <v>17.4</v>
       </c>
       <c r="J96">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K96">
         <v>0</v>
@@ -3764,20 +4469,20 @@
       <c r="A97">
         <v>49001</v>
       </c>
-      <c r="B97">
-        <v>2014</v>
-      </c>
-      <c r="C97">
-        <v>6</v>
-      </c>
-      <c r="D97">
-        <v>217.27000000000001</v>
+      <c r="B97" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" t="s">
+        <v>112</v>
+      </c>
+      <c r="D97" t="s">
+        <v>113</v>
       </c>
       <c r="E97">
-        <v>204.34</v>
+        <v>204.27000000000001</v>
       </c>
       <c r="F97">
-        <v>210.69</v>
+        <v>210.68000000000001</v>
       </c>
       <c r="G97">
         <v>209.80000000000001</v>
@@ -3799,32 +4504,32 @@
       <c r="A98">
         <v>49002</v>
       </c>
-      <c r="B98">
-        <v>2014</v>
-      </c>
-      <c r="C98">
-        <v>6</v>
-      </c>
-      <c r="D98">
-        <v>223.44</v>
+      <c r="B98" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" t="s">
+        <v>112</v>
+      </c>
+      <c r="D98" t="s">
+        <v>114</v>
       </c>
       <c r="E98">
-        <v>207.87</v>
+        <v>205.96000000000001</v>
       </c>
       <c r="F98">
-        <v>215.94999999999999</v>
+        <v>213.21000000000001</v>
       </c>
       <c r="G98">
-        <v>225.61000000000001</v>
+        <v>216.69999999999999</v>
       </c>
       <c r="H98">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="I98">
         <v>21.9</v>
       </c>
       <c r="J98">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K98">
         <v>0</v>
@@ -3834,20 +4539,20 @@
       <c r="A99">
         <v>49003</v>
       </c>
-      <c r="B99">
-        <v>2014</v>
-      </c>
-      <c r="C99">
-        <v>6</v>
-      </c>
-      <c r="D99">
-        <v>220.38</v>
+      <c r="B99" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" t="s">
+        <v>112</v>
+      </c>
+      <c r="D99" t="s">
+        <v>115</v>
       </c>
       <c r="E99">
-        <v>206.47999999999999</v>
+        <v>207.039999999999992</v>
       </c>
       <c r="F99">
-        <v>213.81</v>
+        <v>213.80000000000001</v>
       </c>
       <c r="G99">
         <v>214.94</v>
@@ -3869,20 +4574,20 @@
       <c r="A100">
         <v>49004</v>
       </c>
-      <c r="B100">
-        <v>2014</v>
-      </c>
-      <c r="C100">
-        <v>6</v>
-      </c>
-      <c r="D100">
-        <v>219.46000000000001</v>
+      <c r="B100" t="s">
+        <v>11</v>
+      </c>
+      <c r="C100" t="s">
+        <v>112</v>
+      </c>
+      <c r="D100" t="s">
+        <v>116</v>
       </c>
       <c r="E100">
-        <v>206.74000000000001</v>
+        <v>205.53</v>
       </c>
       <c r="F100">
-        <v>212.31999999999999</v>
+        <v>212.33000000000001</v>
       </c>
       <c r="G100">
         <v>218.41999999999999</v>
@@ -3894,7 +4599,7 @@
         <v>21.9</v>
       </c>
       <c r="J100">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K100">
         <v>0</v>
@@ -3904,17 +4609,17 @@
       <c r="A101">
         <v>49005</v>
       </c>
-      <c r="B101">
-        <v>2014</v>
-      </c>
-      <c r="C101">
-        <v>6</v>
-      </c>
-      <c r="D101">
-        <v>219.69</v>
+      <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" t="s">
+        <v>112</v>
+      </c>
+      <c r="D101" t="s">
+        <v>117</v>
       </c>
       <c r="E101">
-        <v>206.38999999999999</v>
+        <v>206.21000000000001</v>
       </c>
       <c r="F101">
         <v>213.53</v>
@@ -3929,7 +4634,7 @@
         <v>21.8</v>
       </c>
       <c r="J101">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K101">
         <v>0</v>
@@ -3939,23 +4644,23 @@
       <c r="A102">
         <v>49006</v>
       </c>
-      <c r="B102">
-        <v>2014</v>
-      </c>
-      <c r="C102">
-        <v>6</v>
-      </c>
-      <c r="D102">
-        <v>214.59999999999999</v>
+      <c r="B102" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" t="s">
+        <v>112</v>
+      </c>
+      <c r="D102" t="s">
+        <v>118</v>
       </c>
       <c r="E102">
-        <v>202.34999999999999</v>
+        <v>202.46000000000001</v>
       </c>
       <c r="F102">
         <v>207.84</v>
       </c>
       <c r="G102">
-        <v>205.37</v>
+        <v>200.02000000000001</v>
       </c>
       <c r="H102">
         <v>0.34</v>
@@ -3974,29 +4679,29 @@
       <c r="A103">
         <v>49007</v>
       </c>
-      <c r="B103">
-        <v>2014</v>
-      </c>
-      <c r="C103">
-        <v>6</v>
-      </c>
-      <c r="D103">
-        <v>220.47</v>
+      <c r="B103" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103" t="s">
+        <v>112</v>
+      </c>
+      <c r="D103" t="s">
+        <v>119</v>
       </c>
       <c r="E103">
-        <v>207.27000000000001</v>
+        <v>205.94</v>
       </c>
       <c r="F103">
-        <v>214.19</v>
+        <v>212.97</v>
       </c>
       <c r="G103">
-        <v>215.69</v>
+        <v>216.78</v>
       </c>
       <c r="H103">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="I103">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="J103">
         <v>36</v>
@@ -4009,20 +4714,20 @@
       <c r="A104">
         <v>49008</v>
       </c>
-      <c r="B104">
-        <v>2014</v>
-      </c>
-      <c r="C104">
-        <v>6</v>
-      </c>
-      <c r="D104">
-        <v>218.34999999999999</v>
+      <c r="B104" t="s">
+        <v>11</v>
+      </c>
+      <c r="C104" t="s">
+        <v>112</v>
+      </c>
+      <c r="D104" t="s">
+        <v>120</v>
       </c>
       <c r="E104">
         <v>205.52000000000001</v>
       </c>
       <c r="F104">
-        <v>212.40000000000001</v>
+        <v>212.38999999999999</v>
       </c>
       <c r="G104">
         <v>210.94999999999999</v>
@@ -4044,23 +4749,23 @@
       <c r="A105">
         <v>49009</v>
       </c>
-      <c r="B105">
-        <v>2014</v>
-      </c>
-      <c r="C105">
-        <v>6</v>
-      </c>
-      <c r="D105">
-        <v>219.18000000000001</v>
+      <c r="B105" t="s">
+        <v>11</v>
+      </c>
+      <c r="C105" t="s">
+        <v>112</v>
+      </c>
+      <c r="D105" t="s">
+        <v>121</v>
       </c>
       <c r="E105">
-        <v>206.84</v>
+        <v>206.050000000000011</v>
       </c>
       <c r="F105">
-        <v>213.56</v>
+        <v>212.69</v>
       </c>
       <c r="G105">
-        <v>212.63</v>
+        <v>212.96000000000001</v>
       </c>
       <c r="H105">
         <v>0.33</v>
@@ -4079,23 +4784,23 @@
       <c r="A106">
         <v>49010</v>
       </c>
-      <c r="B106">
-        <v>2014</v>
-      </c>
-      <c r="C106">
-        <v>6</v>
-      </c>
-      <c r="D106">
-        <v>219.11000000000001</v>
+      <c r="B106" t="s">
+        <v>11</v>
+      </c>
+      <c r="C106" t="s">
+        <v>112</v>
+      </c>
+      <c r="D106" t="s">
+        <v>122</v>
       </c>
       <c r="E106">
-        <v>207.43000000000001</v>
+        <v>206.94999999999999</v>
       </c>
       <c r="F106">
-        <v>212.55000000000001</v>
+        <v>211.94</v>
       </c>
       <c r="G106">
-        <v>209.84</v>
+        <v>203.94999999999999</v>
       </c>
       <c r="H106">
         <v>0.33</v>
@@ -4114,23 +4819,23 @@
       <c r="A107">
         <v>49011</v>
       </c>
-      <c r="B107">
-        <v>2014</v>
-      </c>
-      <c r="C107">
-        <v>6</v>
-      </c>
-      <c r="D107">
-        <v>216.69999999999999</v>
+      <c r="B107" t="s">
+        <v>11</v>
+      </c>
+      <c r="C107" t="s">
+        <v>112</v>
+      </c>
+      <c r="D107" t="s">
+        <v>123</v>
       </c>
       <c r="E107">
-        <v>204.53999999999999</v>
+        <v>203.53</v>
       </c>
       <c r="F107">
         <v>209.40000000000001</v>
       </c>
       <c r="G107">
-        <v>213.24000000000001</v>
+        <v>211.030000000000001</v>
       </c>
       <c r="H107">
         <v>0.32</v>
@@ -4149,23 +4854,23 @@
       <c r="A108">
         <v>49012</v>
       </c>
-      <c r="B108">
-        <v>2014</v>
-      </c>
-      <c r="C108">
-        <v>6</v>
-      </c>
-      <c r="D108">
-        <v>218.46000000000001</v>
+      <c r="B108" t="s">
+        <v>11</v>
+      </c>
+      <c r="C108" t="s">
+        <v>112</v>
+      </c>
+      <c r="D108" t="s">
+        <v>124</v>
       </c>
       <c r="E108">
         <v>204.63999999999999</v>
       </c>
       <c r="F108">
-        <v>211.90000000000001</v>
+        <v>211.91</v>
       </c>
       <c r="G108">
-        <v>214.84999999999999</v>
+        <v>217.13999999999999</v>
       </c>
       <c r="H108">
         <v>0.31</v>
@@ -4184,23 +4889,23 @@
       <c r="A109">
         <v>49013</v>
       </c>
-      <c r="B109">
-        <v>2014</v>
-      </c>
-      <c r="C109">
-        <v>6</v>
-      </c>
-      <c r="D109">
-        <v>217.97999999999999</v>
+      <c r="B109" t="s">
+        <v>11</v>
+      </c>
+      <c r="C109" t="s">
+        <v>112</v>
+      </c>
+      <c r="D109" t="s">
+        <v>125</v>
       </c>
       <c r="E109">
-        <v>205.34999999999999</v>
+        <v>205.15000000000001</v>
       </c>
       <c r="F109">
-        <v>211.28999999999999</v>
+        <v>211.30000000000001</v>
       </c>
       <c r="G109">
-        <v>207.49000000000001</v>
+        <v>209.90000000000001</v>
       </c>
       <c r="H109">
         <v>0.33</v>
@@ -4219,23 +4924,23 @@
       <c r="A110">
         <v>49014</v>
       </c>
-      <c r="B110">
-        <v>2014</v>
-      </c>
-      <c r="C110">
-        <v>6</v>
-      </c>
-      <c r="D110">
-        <v>214.66999999999999</v>
+      <c r="B110" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110" t="s">
+        <v>112</v>
+      </c>
+      <c r="D110" t="s">
+        <v>126</v>
       </c>
       <c r="E110">
-        <v>202.34999999999999</v>
+        <v>202.22</v>
       </c>
       <c r="F110">
         <v>208.43000000000001</v>
       </c>
       <c r="G110">
-        <v>203.28</v>
+        <v>206.44999999999999</v>
       </c>
       <c r="H110">
         <v>0.33</v>
@@ -4254,29 +4959,29 @@
       <c r="A111">
         <v>49017</v>
       </c>
-      <c r="B111">
-        <v>2014</v>
-      </c>
-      <c r="C111">
-        <v>6</v>
-      </c>
-      <c r="D111">
-        <v>219.91</v>
+      <c r="B111" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" t="s">
+        <v>112</v>
+      </c>
+      <c r="D111" t="s">
+        <v>113</v>
       </c>
       <c r="E111">
-        <v>206.53999999999999</v>
+        <v>204.94999999999999</v>
       </c>
       <c r="F111">
-        <v>213.5</v>
+        <v>211.0</v>
       </c>
       <c r="G111">
-        <v>215.80000000000001</v>
+        <v>209.25</v>
       </c>
       <c r="H111">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="I111">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="J111">
         <v>36</v>
@@ -4289,29 +4994,29 @@
       <c r="A112">
         <v>49018</v>
       </c>
-      <c r="B112">
-        <v>2014</v>
-      </c>
-      <c r="C112">
-        <v>6</v>
-      </c>
-      <c r="D112">
-        <v>217.49000000000001</v>
+      <c r="B112" t="s">
+        <v>11</v>
+      </c>
+      <c r="C112" t="s">
+        <v>112</v>
+      </c>
+      <c r="D112" t="s">
+        <v>127</v>
       </c>
       <c r="E112">
-        <v>204.22</v>
+        <v>203.59</v>
       </c>
       <c r="F112">
-        <v>211.0</v>
+        <v>210.38999999999999</v>
       </c>
       <c r="G112">
-        <v>214.88</v>
+        <v>215.87</v>
       </c>
       <c r="H112">
         <v>0.31</v>
       </c>
       <c r="I112">
-        <v>21.7</v>
+        <v>22.0</v>
       </c>
       <c r="J112">
         <v>36</v>
@@ -4324,23 +5029,23 @@
       <c r="A113">
         <v>49019</v>
       </c>
-      <c r="B113">
-        <v>2014</v>
-      </c>
-      <c r="C113">
-        <v>6</v>
-      </c>
-      <c r="D113">
-        <v>212.84999999999999</v>
+      <c r="B113" t="s">
+        <v>11</v>
+      </c>
+      <c r="C113" t="s">
+        <v>112</v>
+      </c>
+      <c r="D113" t="s">
+        <v>128</v>
       </c>
       <c r="E113">
-        <v>204.24000000000001</v>
+        <v>204.41</v>
       </c>
       <c r="F113">
-        <v>208.28</v>
+        <v>209.25</v>
       </c>
       <c r="G113">
-        <v>197.21000000000001</v>
+        <v>205.099999999999994</v>
       </c>
       <c r="H113">
         <v>0.33</v>
@@ -4349,7 +5054,7 @@
         <v>21.2</v>
       </c>
       <c r="J113">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K113">
         <v>0</v>
@@ -4359,14 +5064,14 @@
       <c r="A114">
         <v>49020</v>
       </c>
-      <c r="B114">
-        <v>2014</v>
-      </c>
-      <c r="C114">
-        <v>6</v>
-      </c>
-      <c r="D114">
-        <v>216.72999999999999</v>
+      <c r="B114" t="s">
+        <v>11</v>
+      </c>
+      <c r="C114" t="s">
+        <v>112</v>
+      </c>
+      <c r="D114" t="s">
+        <v>129</v>
       </c>
       <c r="E114">
         <v>202.81999999999999</v>
@@ -4375,7 +5080,7 @@
         <v>209.74000000000001</v>
       </c>
       <c r="G114">
-        <v>209.71000000000001</v>
+        <v>206.88</v>
       </c>
       <c r="H114">
         <v>0.33</v>
@@ -4394,32 +5099,32 @@
       <c r="A115">
         <v>49021</v>
       </c>
-      <c r="B115">
-        <v>2014</v>
-      </c>
-      <c r="C115">
-        <v>6</v>
-      </c>
-      <c r="D115">
-        <v>211.72</v>
+      <c r="B115" t="s">
+        <v>11</v>
+      </c>
+      <c r="C115" t="s">
+        <v>112</v>
+      </c>
+      <c r="D115" t="s">
+        <v>130</v>
       </c>
       <c r="E115">
-        <v>203.72999999999999</v>
+        <v>204.49000000000001</v>
       </c>
       <c r="F115">
-        <v>207.43000000000001</v>
+        <v>210.069999999999993</v>
       </c>
       <c r="G115">
-        <v>194.28</v>
+        <v>208.83000000000001</v>
       </c>
       <c r="H115">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="I115">
         <v>21.9</v>
       </c>
       <c r="J115">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K115">
         <v>0</v>
@@ -4429,23 +5134,23 @@
       <c r="A116">
         <v>49001</v>
       </c>
-      <c r="B116">
-        <v>2014</v>
-      </c>
-      <c r="C116">
-        <v>7</v>
-      </c>
-      <c r="D116">
-        <v>197.080000000000013</v>
+      <c r="B116" t="s">
+        <v>11</v>
+      </c>
+      <c r="C116" t="s">
+        <v>131</v>
+      </c>
+      <c r="D116" t="s">
+        <v>132</v>
       </c>
       <c r="E116">
-        <v>188.50999999999999</v>
+        <v>188.46000000000001</v>
       </c>
       <c r="F116">
         <v>193.5</v>
       </c>
       <c r="G116">
-        <v>172.69</v>
+        <v>173.050000000000011</v>
       </c>
       <c r="H116">
         <v>0.41</v>
@@ -4464,32 +5169,32 @@
       <c r="A117">
         <v>49002</v>
       </c>
-      <c r="B117">
-        <v>2014</v>
-      </c>
-      <c r="C117">
-        <v>7</v>
-      </c>
-      <c r="D117">
-        <v>215.66999999999999</v>
+      <c r="B117" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D117" t="s">
+        <v>133</v>
       </c>
       <c r="E117">
-        <v>206.19</v>
+        <v>202.72999999999999</v>
       </c>
       <c r="F117">
-        <v>212.78</v>
+        <v>208.69999999999999</v>
       </c>
       <c r="G117">
-        <v>208.24000000000001</v>
+        <v>202.11000000000001</v>
       </c>
       <c r="H117">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="I117">
         <v>22.6</v>
       </c>
       <c r="J117">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K117">
         <v>0</v>
@@ -4499,20 +5204,20 @@
       <c r="A118">
         <v>49003</v>
       </c>
-      <c r="B118">
-        <v>2014</v>
-      </c>
-      <c r="C118">
-        <v>7</v>
-      </c>
-      <c r="D118">
-        <v>211.38</v>
+      <c r="B118" t="s">
+        <v>11</v>
+      </c>
+      <c r="C118" t="s">
+        <v>131</v>
+      </c>
+      <c r="D118" t="s">
+        <v>134</v>
       </c>
       <c r="E118">
-        <v>202.88</v>
+        <v>203.34</v>
       </c>
       <c r="F118">
-        <v>208.83000000000001</v>
+        <v>208.81999999999999</v>
       </c>
       <c r="G118">
         <v>205.050000000000011</v>
@@ -4534,23 +5239,23 @@
       <c r="A119">
         <v>49004</v>
       </c>
-      <c r="B119">
-        <v>2014</v>
-      </c>
-      <c r="C119">
-        <v>7</v>
-      </c>
-      <c r="D119">
-        <v>209.25999999999999</v>
+      <c r="B119" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119" t="s">
+        <v>131</v>
+      </c>
+      <c r="D119" t="s">
+        <v>135</v>
       </c>
       <c r="E119">
-        <v>201.59999999999999</v>
+        <v>200.63</v>
       </c>
       <c r="F119">
         <v>206.16</v>
       </c>
       <c r="G119">
-        <v>204.90000000000001</v>
+        <v>205.69</v>
       </c>
       <c r="H119">
         <v>0.33</v>
@@ -4559,7 +5264,7 @@
         <v>22.9</v>
       </c>
       <c r="J119">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K119">
         <v>0</v>
@@ -4569,17 +5274,17 @@
       <c r="A120">
         <v>49005</v>
       </c>
-      <c r="B120">
-        <v>2014</v>
-      </c>
-      <c r="C120">
-        <v>7</v>
-      </c>
-      <c r="D120">
-        <v>203.86000000000001</v>
+      <c r="B120" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120" t="s">
+        <v>131</v>
+      </c>
+      <c r="D120" t="s">
+        <v>136</v>
       </c>
       <c r="E120">
-        <v>196.16999999999999</v>
+        <v>196.02000000000001</v>
       </c>
       <c r="F120">
         <v>201.80000000000001</v>
@@ -4594,7 +5299,7 @@
         <v>22.8</v>
       </c>
       <c r="J120">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K120">
         <v>0</v>
@@ -4604,23 +5309,23 @@
       <c r="A121">
         <v>49006</v>
       </c>
-      <c r="B121">
-        <v>2014</v>
-      </c>
-      <c r="C121">
-        <v>7</v>
-      </c>
-      <c r="D121">
-        <v>204.44</v>
+      <c r="B121" t="s">
+        <v>11</v>
+      </c>
+      <c r="C121" t="s">
+        <v>131</v>
+      </c>
+      <c r="D121" t="s">
+        <v>137</v>
       </c>
       <c r="E121">
-        <v>196.49000000000001</v>
+        <v>196.56999999999999</v>
       </c>
       <c r="F121">
         <v>201.02000000000001</v>
       </c>
       <c r="G121">
-        <v>184.87</v>
+        <v>184.25</v>
       </c>
       <c r="H121">
         <v>0.39</v>
@@ -4639,23 +5344,23 @@
       <c r="A122">
         <v>49007</v>
       </c>
-      <c r="B122">
-        <v>2014</v>
-      </c>
-      <c r="C122">
-        <v>7</v>
-      </c>
-      <c r="D122">
-        <v>201.77000000000001</v>
+      <c r="B122" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" t="s">
+        <v>131</v>
+      </c>
+      <c r="D122" t="s">
+        <v>138</v>
       </c>
       <c r="E122">
-        <v>193.16</v>
+        <v>192.34</v>
       </c>
       <c r="F122">
-        <v>198.66</v>
+        <v>197.87</v>
       </c>
       <c r="G122">
-        <v>187.31999999999999</v>
+        <v>184.71000000000001</v>
       </c>
       <c r="H122">
         <v>0.38</v>
@@ -4674,14 +5379,14 @@
       <c r="A123">
         <v>49008</v>
       </c>
-      <c r="B123">
-        <v>2014</v>
-      </c>
-      <c r="C123">
-        <v>7</v>
-      </c>
-      <c r="D123">
-        <v>194.52000000000001</v>
+      <c r="B123" t="s">
+        <v>11</v>
+      </c>
+      <c r="C123" t="s">
+        <v>131</v>
+      </c>
+      <c r="D123" t="s">
+        <v>139</v>
       </c>
       <c r="E123">
         <v>186.24000000000001</v>
@@ -4709,26 +5414,26 @@
       <c r="A124">
         <v>49009</v>
       </c>
-      <c r="B124">
-        <v>2014</v>
-      </c>
-      <c r="C124">
-        <v>7</v>
-      </c>
-      <c r="D124">
-        <v>195.75</v>
+      <c r="B124" t="s">
+        <v>11</v>
+      </c>
+      <c r="C124" t="s">
+        <v>131</v>
+      </c>
+      <c r="D124" t="s">
+        <v>140</v>
       </c>
       <c r="E124">
-        <v>187.49000000000001</v>
+        <v>189.87</v>
       </c>
       <c r="F124">
-        <v>192.71000000000001</v>
+        <v>195.13999999999999</v>
       </c>
       <c r="G124">
-        <v>177.46000000000001</v>
+        <v>185.43000000000001</v>
       </c>
       <c r="H124">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="I124">
         <v>22.0</v>
@@ -4744,23 +5449,23 @@
       <c r="A125">
         <v>49010</v>
       </c>
-      <c r="B125">
-        <v>2014</v>
-      </c>
-      <c r="C125">
-        <v>7</v>
-      </c>
-      <c r="D125">
-        <v>208.50999999999999</v>
+      <c r="B125" t="s">
+        <v>11</v>
+      </c>
+      <c r="C125" t="s">
+        <v>131</v>
+      </c>
+      <c r="D125" t="s">
+        <v>141</v>
       </c>
       <c r="E125">
-        <v>201.93000000000001</v>
+        <v>201.37</v>
       </c>
       <c r="F125">
-        <v>206.02000000000001</v>
+        <v>205.36000000000001</v>
       </c>
       <c r="G125">
-        <v>195.039999999999992</v>
+        <v>189.94</v>
       </c>
       <c r="H125">
         <v>0.35</v>
@@ -4779,23 +5484,23 @@
       <c r="A126">
         <v>49011</v>
       </c>
-      <c r="B126">
-        <v>2014</v>
-      </c>
-      <c r="C126">
-        <v>7</v>
-      </c>
-      <c r="D126">
-        <v>198.91999999999999</v>
+      <c r="B126" t="s">
+        <v>11</v>
+      </c>
+      <c r="C126" t="s">
+        <v>131</v>
+      </c>
+      <c r="D126" t="s">
+        <v>142</v>
       </c>
       <c r="E126">
-        <v>191.46000000000001</v>
+        <v>190.69</v>
       </c>
       <c r="F126">
-        <v>195.27000000000001</v>
+        <v>195.25999999999999</v>
       </c>
       <c r="G126">
-        <v>186.78999999999999</v>
+        <v>184.41999999999999</v>
       </c>
       <c r="H126">
         <v>0.36</v>
@@ -4814,23 +5519,23 @@
       <c r="A127">
         <v>49012</v>
       </c>
-      <c r="B127">
-        <v>2014</v>
-      </c>
-      <c r="C127">
-        <v>7</v>
-      </c>
-      <c r="D127">
-        <v>209.81</v>
+      <c r="B127" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127" t="s">
+        <v>131</v>
+      </c>
+      <c r="D127" t="s">
+        <v>143</v>
       </c>
       <c r="E127">
         <v>200.66</v>
       </c>
       <c r="F127">
-        <v>206.68000000000001</v>
+        <v>206.69999999999999</v>
       </c>
       <c r="G127">
-        <v>206.83000000000001</v>
+        <v>207.59</v>
       </c>
       <c r="H127">
         <v>0.32</v>
@@ -4849,26 +5554,26 @@
       <c r="A128">
         <v>49013</v>
       </c>
-      <c r="B128">
-        <v>2014</v>
-      </c>
-      <c r="C128">
-        <v>7</v>
-      </c>
-      <c r="D128">
-        <v>206.11000000000001</v>
+      <c r="B128" t="s">
+        <v>11</v>
+      </c>
+      <c r="C128" t="s">
+        <v>131</v>
+      </c>
+      <c r="D128" t="s">
+        <v>144</v>
       </c>
       <c r="E128">
-        <v>198.78999999999999</v>
+        <v>198.63</v>
       </c>
       <c r="F128">
         <v>203.65000000000001</v>
       </c>
       <c r="G128">
-        <v>190.46000000000001</v>
+        <v>195.47999999999999</v>
       </c>
       <c r="H128">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="I128">
         <v>22.9</v>
@@ -4884,23 +5589,23 @@
       <c r="A129">
         <v>49014</v>
       </c>
-      <c r="B129">
-        <v>2014</v>
-      </c>
-      <c r="C129">
-        <v>7</v>
-      </c>
-      <c r="D129">
-        <v>203.58000000000001</v>
+      <c r="B129" t="s">
+        <v>11</v>
+      </c>
+      <c r="C129" t="s">
+        <v>131</v>
+      </c>
+      <c r="D129" t="s">
+        <v>145</v>
       </c>
       <c r="E129">
-        <v>195.81</v>
+        <v>195.71000000000001</v>
       </c>
       <c r="F129">
-        <v>200.75999999999999</v>
+        <v>200.75</v>
       </c>
       <c r="G129">
-        <v>189.66999999999999</v>
+        <v>190.75</v>
       </c>
       <c r="H129">
         <v>0.35</v>
@@ -4919,29 +5624,29 @@
       <c r="A130">
         <v>49017</v>
       </c>
-      <c r="B130">
-        <v>2014</v>
-      </c>
-      <c r="C130">
-        <v>7</v>
-      </c>
-      <c r="D130">
-        <v>199.84</v>
+      <c r="B130" t="s">
+        <v>11</v>
+      </c>
+      <c r="C130" t="s">
+        <v>131</v>
+      </c>
+      <c r="D130" t="s">
+        <v>146</v>
       </c>
       <c r="E130">
-        <v>191.30000000000001</v>
+        <v>186.97999999999999</v>
       </c>
       <c r="F130">
-        <v>196.72999999999999</v>
+        <v>191.66999999999999</v>
       </c>
       <c r="G130">
-        <v>181.81</v>
+        <v>171.16</v>
       </c>
       <c r="H130">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="I130">
-        <v>22.5</v>
+        <v>22.0</v>
       </c>
       <c r="J130">
         <v>36</v>
@@ -4954,29 +5659,29 @@
       <c r="A131">
         <v>49018</v>
       </c>
-      <c r="B131">
-        <v>2014</v>
-      </c>
-      <c r="C131">
-        <v>7</v>
-      </c>
-      <c r="D131">
-        <v>207.34999999999999</v>
+      <c r="B131" t="s">
+        <v>11</v>
+      </c>
+      <c r="C131" t="s">
+        <v>131</v>
+      </c>
+      <c r="D131" t="s">
+        <v>147</v>
       </c>
       <c r="E131">
-        <v>198.94999999999999</v>
+        <v>201.16999999999999</v>
       </c>
       <c r="F131">
-        <v>204.50999999999999</v>
+        <v>206.84</v>
       </c>
       <c r="G131">
-        <v>202.55000000000001</v>
+        <v>205.78</v>
       </c>
       <c r="H131">
         <v>0.33</v>
       </c>
       <c r="I131">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="J131">
         <v>36</v>
@@ -4989,32 +5694,32 @@
       <c r="A132">
         <v>49019</v>
       </c>
-      <c r="B132">
-        <v>2014</v>
-      </c>
-      <c r="C132">
-        <v>7</v>
-      </c>
-      <c r="D132">
-        <v>202.87</v>
+      <c r="B132" t="s">
+        <v>11</v>
+      </c>
+      <c r="C132" t="s">
+        <v>131</v>
+      </c>
+      <c r="D132" t="s">
+        <v>148</v>
       </c>
       <c r="E132">
-        <v>197.94</v>
+        <v>198.44</v>
       </c>
       <c r="F132">
-        <v>201.31999999999999</v>
+        <v>202.52000000000001</v>
       </c>
       <c r="G132">
-        <v>175.080000000000013</v>
+        <v>184.94999999999999</v>
       </c>
       <c r="H132">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="I132">
         <v>21.9</v>
       </c>
       <c r="J132">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -5024,14 +5729,14 @@
       <c r="A133">
         <v>49020</v>
       </c>
-      <c r="B133">
-        <v>2014</v>
-      </c>
-      <c r="C133">
-        <v>7</v>
-      </c>
-      <c r="D133">
-        <v>207.5</v>
+      <c r="B133" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133" t="s">
+        <v>131</v>
+      </c>
+      <c r="D133" t="s">
+        <v>149</v>
       </c>
       <c r="E133">
         <v>198.78</v>
@@ -5040,7 +5745,7 @@
         <v>204.41</v>
       </c>
       <c r="G133">
-        <v>190.49000000000001</v>
+        <v>188.13</v>
       </c>
       <c r="H133">
         <v>0.37</v>
@@ -5059,32 +5764,32 @@
       <c r="A134">
         <v>49021</v>
       </c>
-      <c r="B134">
-        <v>2014</v>
-      </c>
-      <c r="C134">
-        <v>7</v>
-      </c>
-      <c r="D134">
-        <v>199.11000000000001</v>
+      <c r="B134" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134" t="s">
+        <v>131</v>
+      </c>
+      <c r="D134" t="s">
+        <v>150</v>
       </c>
       <c r="E134">
-        <v>194.94</v>
+        <v>197.62</v>
       </c>
       <c r="F134">
-        <v>197.97</v>
+        <v>202.22999999999999</v>
       </c>
       <c r="G134">
-        <v>175.77000000000001</v>
+        <v>195.030000000000001</v>
       </c>
       <c r="H134">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="I134">
         <v>22.9</v>
       </c>
       <c r="J134">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K134">
         <v>0</v>
@@ -5094,20 +5799,20 @@
       <c r="A135">
         <v>49001</v>
       </c>
-      <c r="B135">
-        <v>2014</v>
-      </c>
-      <c r="C135">
-        <v>8</v>
-      </c>
-      <c r="D135">
-        <v>199.94999999999999</v>
+      <c r="B135" t="s">
+        <v>11</v>
+      </c>
+      <c r="C135" t="s">
+        <v>151</v>
+      </c>
+      <c r="D135" t="s">
+        <v>152</v>
       </c>
       <c r="E135">
-        <v>212.28999999999999</v>
+        <v>212.25999999999999</v>
       </c>
       <c r="F135">
-        <v>214.47</v>
+        <v>214.46000000000001</v>
       </c>
       <c r="G135">
         <v>207.94999999999999</v>
@@ -5129,32 +5834,32 @@
       <c r="A136">
         <v>49002</v>
       </c>
-      <c r="B136">
-        <v>2014</v>
-      </c>
-      <c r="C136">
-        <v>8</v>
-      </c>
-      <c r="D136">
-        <v>207.31999999999999</v>
+      <c r="B136" t="s">
+        <v>11</v>
+      </c>
+      <c r="C136" t="s">
+        <v>151</v>
+      </c>
+      <c r="D136" t="s">
+        <v>153</v>
       </c>
       <c r="E136">
-        <v>220.039999999999992</v>
+        <v>216.88</v>
       </c>
       <c r="F136">
-        <v>222.91</v>
+        <v>219.41999999999999</v>
       </c>
       <c r="G136">
-        <v>226.19999999999999</v>
+        <v>219.030000000000001</v>
       </c>
       <c r="H136">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="I136">
         <v>23.1</v>
       </c>
       <c r="J136">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K136">
         <v>0</v>
@@ -5164,23 +5869,23 @@
       <c r="A137">
         <v>49003</v>
       </c>
-      <c r="B137">
-        <v>2014</v>
-      </c>
-      <c r="C137">
-        <v>8</v>
-      </c>
-      <c r="D137">
-        <v>203.86000000000001</v>
+      <c r="B137" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" t="s">
+        <v>151</v>
+      </c>
+      <c r="D137" t="s">
+        <v>154</v>
       </c>
       <c r="E137">
-        <v>216.97</v>
+        <v>217.21000000000001</v>
       </c>
       <c r="F137">
-        <v>219.52000000000001</v>
+        <v>219.50999999999999</v>
       </c>
       <c r="G137">
-        <v>220.18000000000001</v>
+        <v>220.44</v>
       </c>
       <c r="H137">
         <v>0.3</v>
@@ -5199,23 +5904,23 @@
       <c r="A138">
         <v>49004</v>
       </c>
-      <c r="B138">
-        <v>2014</v>
-      </c>
-      <c r="C138">
-        <v>8</v>
-      </c>
-      <c r="D138">
-        <v>200.38999999999999</v>
+      <c r="B138" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" t="s">
+        <v>151</v>
+      </c>
+      <c r="D138" t="s">
+        <v>155</v>
       </c>
       <c r="E138">
-        <v>213.47</v>
+        <v>212.97</v>
       </c>
       <c r="F138">
-        <v>215.28999999999999</v>
+        <v>215.30000000000001</v>
       </c>
       <c r="G138">
-        <v>211.72999999999999</v>
+        <v>211.90000000000001</v>
       </c>
       <c r="H138">
         <v>0.31</v>
@@ -5224,7 +5929,7 @@
         <v>23.9</v>
       </c>
       <c r="J138">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K138">
         <v>0</v>
@@ -5234,23 +5939,23 @@
       <c r="A139">
         <v>49005</v>
       </c>
-      <c r="B139">
-        <v>2014</v>
-      </c>
-      <c r="C139">
-        <v>8</v>
-      </c>
-      <c r="D139">
-        <v>201.41</v>
+      <c r="B139" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139" t="s">
+        <v>151</v>
+      </c>
+      <c r="D139" t="s">
+        <v>156</v>
       </c>
       <c r="E139">
-        <v>214.81999999999999</v>
+        <v>214.75999999999999</v>
       </c>
       <c r="F139">
-        <v>217.25</v>
+        <v>217.28</v>
       </c>
       <c r="G139">
-        <v>215.87</v>
+        <v>216.21000000000001</v>
       </c>
       <c r="H139">
         <v>0.3</v>
@@ -5259,7 +5964,7 @@
         <v>23.7</v>
       </c>
       <c r="J139">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K139">
         <v>0</v>
@@ -5269,23 +5974,23 @@
       <c r="A140">
         <v>49006</v>
       </c>
-      <c r="B140">
-        <v>2014</v>
-      </c>
-      <c r="C140">
-        <v>8</v>
-      </c>
-      <c r="D140">
-        <v>198.34999999999999</v>
+      <c r="B140" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" t="s">
+        <v>151</v>
+      </c>
+      <c r="D140" t="s">
+        <v>157</v>
       </c>
       <c r="E140">
-        <v>210.53999999999999</v>
+        <v>210.59</v>
       </c>
       <c r="F140">
-        <v>212.41999999999999</v>
+        <v>212.40000000000001</v>
       </c>
       <c r="G140">
-        <v>203.91</v>
+        <v>204.43000000000001</v>
       </c>
       <c r="H140">
         <v>0.34</v>
@@ -5304,29 +6009,29 @@
       <c r="A141">
         <v>49007</v>
       </c>
-      <c r="B141">
-        <v>2014</v>
-      </c>
-      <c r="C141">
-        <v>8</v>
-      </c>
-      <c r="D141">
-        <v>201.75</v>
+      <c r="B141" t="s">
+        <v>11</v>
+      </c>
+      <c r="C141" t="s">
+        <v>151</v>
+      </c>
+      <c r="D141" t="s">
+        <v>158</v>
       </c>
       <c r="E141">
-        <v>214.69</v>
+        <v>214.65000000000001</v>
       </c>
       <c r="F141">
         <v>217.030000000000001</v>
       </c>
       <c r="G141">
-        <v>213.37</v>
+        <v>214.71000000000001</v>
       </c>
       <c r="H141">
         <v>0.32</v>
       </c>
       <c r="I141">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="J141">
         <v>36</v>
@@ -5339,14 +6044,14 @@
       <c r="A142">
         <v>49008</v>
       </c>
-      <c r="B142">
-        <v>2014</v>
-      </c>
-      <c r="C142">
-        <v>8</v>
-      </c>
-      <c r="D142">
-        <v>185.91</v>
+      <c r="B142" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142" t="s">
+        <v>151</v>
+      </c>
+      <c r="D142" t="s">
+        <v>159</v>
       </c>
       <c r="E142">
         <v>196.34</v>
@@ -5374,26 +6079,26 @@
       <c r="A143">
         <v>49009</v>
       </c>
-      <c r="B143">
-        <v>2014</v>
-      </c>
-      <c r="C143">
-        <v>8</v>
-      </c>
-      <c r="D143">
-        <v>191.66999999999999</v>
+      <c r="B143" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" t="s">
+        <v>151</v>
+      </c>
+      <c r="D143" t="s">
+        <v>160</v>
       </c>
       <c r="E143">
-        <v>203.71000000000001</v>
+        <v>204.87</v>
       </c>
       <c r="F143">
-        <v>205.86000000000001</v>
+        <v>207.0099999999999909</v>
       </c>
       <c r="G143">
-        <v>193.039999999999992</v>
+        <v>196.37</v>
       </c>
       <c r="H143">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="I143">
         <v>22.4</v>
@@ -5409,23 +6114,23 @@
       <c r="A144">
         <v>49010</v>
       </c>
-      <c r="B144">
-        <v>2014</v>
-      </c>
-      <c r="C144">
-        <v>8</v>
-      </c>
-      <c r="D144">
-        <v>198.13</v>
+      <c r="B144" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" t="s">
+        <v>151</v>
+      </c>
+      <c r="D144" t="s">
+        <v>161</v>
       </c>
       <c r="E144">
-        <v>212.34999999999999</v>
+        <v>211.65000000000001</v>
       </c>
       <c r="F144">
-        <v>213.78999999999999</v>
+        <v>213.099999999999994</v>
       </c>
       <c r="G144">
-        <v>193.77000000000001</v>
+        <v>191.81</v>
       </c>
       <c r="H144">
         <v>0.34</v>
@@ -5444,23 +6149,23 @@
       <c r="A145">
         <v>49011</v>
       </c>
-      <c r="B145">
-        <v>2014</v>
-      </c>
-      <c r="C145">
-        <v>8</v>
-      </c>
-      <c r="D145">
-        <v>198.53</v>
+      <c r="B145" t="s">
+        <v>11</v>
+      </c>
+      <c r="C145" t="s">
+        <v>151</v>
+      </c>
+      <c r="D145" t="s">
+        <v>162</v>
       </c>
       <c r="E145">
-        <v>212.0</v>
+        <v>211.56</v>
       </c>
       <c r="F145">
-        <v>213.59</v>
+        <v>213.50999999999999</v>
       </c>
       <c r="G145">
-        <v>204.050000000000011</v>
+        <v>207.71000000000001</v>
       </c>
       <c r="H145">
         <v>0.32</v>
@@ -5479,23 +6184,23 @@
       <c r="A146">
         <v>49012</v>
       </c>
-      <c r="B146">
-        <v>2014</v>
-      </c>
-      <c r="C146">
-        <v>8</v>
-      </c>
-      <c r="D146">
-        <v>203.55000000000001</v>
+      <c r="B146" t="s">
+        <v>11</v>
+      </c>
+      <c r="C146" t="s">
+        <v>151</v>
+      </c>
+      <c r="D146" t="s">
+        <v>163</v>
       </c>
       <c r="E146">
-        <v>216.31</v>
+        <v>216.31999999999999</v>
       </c>
       <c r="F146">
-        <v>218.91</v>
+        <v>218.91999999999999</v>
       </c>
       <c r="G146">
-        <v>223.63</v>
+        <v>223.63999999999999</v>
       </c>
       <c r="H146">
         <v>0.29</v>
@@ -5514,23 +6219,23 @@
       <c r="A147">
         <v>49013</v>
       </c>
-      <c r="B147">
-        <v>2014</v>
-      </c>
-      <c r="C147">
-        <v>8</v>
-      </c>
-      <c r="D147">
-        <v>199.40000000000001</v>
+      <c r="B147" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147" t="s">
+        <v>151</v>
+      </c>
+      <c r="D147" t="s">
+        <v>111</v>
       </c>
       <c r="E147">
-        <v>212.34</v>
+        <v>212.25999999999999</v>
       </c>
       <c r="F147">
-        <v>214.38999999999999</v>
+        <v>214.36000000000001</v>
       </c>
       <c r="G147">
-        <v>198.47</v>
+        <v>203.16</v>
       </c>
       <c r="H147">
         <v>0.34</v>
@@ -5549,17 +6254,17 @@
       <c r="A148">
         <v>49014</v>
       </c>
-      <c r="B148">
-        <v>2014</v>
-      </c>
-      <c r="C148">
-        <v>8</v>
-      </c>
-      <c r="D148">
-        <v>195.12</v>
+      <c r="B148" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148" t="s">
+        <v>151</v>
+      </c>
+      <c r="D148" t="s">
+        <v>164</v>
       </c>
       <c r="E148">
-        <v>206.30000000000001</v>
+        <v>206.24000000000001</v>
       </c>
       <c r="F148">
         <v>208.41</v>
@@ -5584,29 +6289,29 @@
       <c r="A149">
         <v>49017</v>
       </c>
-      <c r="B149">
-        <v>2014</v>
-      </c>
-      <c r="C149">
-        <v>8</v>
-      </c>
-      <c r="D149">
-        <v>199.19</v>
+      <c r="B149" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" t="s">
+        <v>151</v>
+      </c>
+      <c r="D149" t="s">
+        <v>165</v>
       </c>
       <c r="E149">
-        <v>211.46000000000001</v>
+        <v>204.59</v>
       </c>
       <c r="F149">
-        <v>213.81</v>
+        <v>206.61000000000001</v>
       </c>
       <c r="G149">
-        <v>207.59</v>
+        <v>190.68000000000001</v>
       </c>
       <c r="H149">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="I149">
-        <v>23.1</v>
+        <v>22.3</v>
       </c>
       <c r="J149">
         <v>36</v>
@@ -5619,29 +6324,29 @@
       <c r="A150">
         <v>49018</v>
       </c>
-      <c r="B150">
-        <v>2014</v>
-      </c>
-      <c r="C150">
-        <v>8</v>
-      </c>
-      <c r="D150">
-        <v>202.94999999999999</v>
+      <c r="B150" t="s">
+        <v>11</v>
+      </c>
+      <c r="C150" t="s">
+        <v>151</v>
+      </c>
+      <c r="D150" t="s">
+        <v>166</v>
       </c>
       <c r="E150">
-        <v>216.43000000000001</v>
+        <v>213.58000000000001</v>
       </c>
       <c r="F150">
-        <v>218.74000000000001</v>
+        <v>215.91</v>
       </c>
       <c r="G150">
-        <v>219.69</v>
+        <v>215.99000000000001</v>
       </c>
       <c r="H150">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="I150">
-        <v>23.0</v>
+        <v>23.4</v>
       </c>
       <c r="J150">
         <v>36</v>
@@ -5654,23 +6359,23 @@
       <c r="A151">
         <v>49019</v>
       </c>
-      <c r="B151">
-        <v>2014</v>
-      </c>
-      <c r="C151">
-        <v>8</v>
-      </c>
-      <c r="D151">
-        <v>193.49000000000001</v>
+      <c r="B151" t="s">
+        <v>11</v>
+      </c>
+      <c r="C151" t="s">
+        <v>151</v>
+      </c>
+      <c r="D151" t="s">
+        <v>167</v>
       </c>
       <c r="E151">
-        <v>206.96000000000001</v>
+        <v>208.93000000000001</v>
       </c>
       <c r="F151">
-        <v>208.18000000000001</v>
+        <v>210.40000000000001</v>
       </c>
       <c r="G151">
-        <v>187.52000000000001</v>
+        <v>194.72</v>
       </c>
       <c r="H151">
         <v>0.35</v>
@@ -5679,7 +6384,7 @@
         <v>22.3</v>
       </c>
       <c r="J151">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K151">
         <v>0</v>
@@ -5689,17 +6394,17 @@
       <c r="A152">
         <v>49020</v>
       </c>
-      <c r="B152">
-        <v>2014</v>
-      </c>
-      <c r="C152">
-        <v>8</v>
-      </c>
-      <c r="D152">
-        <v>202.34999999999999</v>
+      <c r="B152" t="s">
+        <v>11</v>
+      </c>
+      <c r="C152" t="s">
+        <v>151</v>
+      </c>
+      <c r="D152" t="s">
+        <v>168</v>
       </c>
       <c r="E152">
-        <v>214.38999999999999</v>
+        <v>214.38</v>
       </c>
       <c r="F152">
         <v>216.81999999999999</v>
@@ -5724,32 +6429,32 @@
       <c r="A153">
         <v>49021</v>
       </c>
-      <c r="B153">
-        <v>2014</v>
-      </c>
-      <c r="C153">
-        <v>8</v>
-      </c>
-      <c r="D153">
-        <v>193.97999999999999</v>
+      <c r="B153" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153" t="s">
+        <v>151</v>
+      </c>
+      <c r="D153" t="s">
+        <v>169</v>
       </c>
       <c r="E153">
-        <v>207.56</v>
+        <v>215.69999999999999</v>
       </c>
       <c r="F153">
-        <v>208.66</v>
+        <v>217.53</v>
       </c>
       <c r="G153">
-        <v>188.77000000000001</v>
+        <v>214.90000000000001</v>
       </c>
       <c r="H153">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="I153">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="J153">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K153">
         <v>0</v>
@@ -5759,23 +6464,23 @@
       <c r="A154">
         <v>49001</v>
       </c>
-      <c r="B154">
-        <v>2014</v>
-      </c>
-      <c r="C154">
-        <v>9</v>
-      </c>
-      <c r="D154">
-        <v>139.63999999999999</v>
+      <c r="B154" t="s">
+        <v>11</v>
+      </c>
+      <c r="C154" t="s">
+        <v>170</v>
+      </c>
+      <c r="D154" t="s">
+        <v>171</v>
       </c>
       <c r="E154">
         <v>168.66</v>
       </c>
       <c r="F154">
-        <v>167.099999999999994</v>
+        <v>167.090000000000003</v>
       </c>
       <c r="G154">
-        <v>148.44999999999999</v>
+        <v>148.62</v>
       </c>
       <c r="H154">
         <v>0.41</v>
@@ -5794,32 +6499,32 @@
       <c r="A155">
         <v>49002</v>
       </c>
-      <c r="B155">
-        <v>2014</v>
-      </c>
-      <c r="C155">
-        <v>9</v>
-      </c>
-      <c r="D155">
-        <v>148.58000000000001</v>
+      <c r="B155" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" t="s">
+        <v>170</v>
+      </c>
+      <c r="D155" t="s">
+        <v>172</v>
       </c>
       <c r="E155">
-        <v>182.44</v>
+        <v>181.75</v>
       </c>
       <c r="F155">
-        <v>180.28999999999999</v>
+        <v>179.72</v>
       </c>
       <c r="G155">
-        <v>167.83000000000001</v>
+        <v>166.83000000000001</v>
       </c>
       <c r="H155">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="I155">
         <v>21.0</v>
       </c>
       <c r="J155">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K155">
         <v>0</v>
@@ -5829,20 +6534,20 @@
       <c r="A156">
         <v>49003</v>
       </c>
-      <c r="B156">
-        <v>2014</v>
-      </c>
-      <c r="C156">
-        <v>9</v>
-      </c>
-      <c r="D156">
-        <v>145.65000000000001</v>
+      <c r="B156" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" t="s">
+        <v>170</v>
+      </c>
+      <c r="D156" t="s">
+        <v>173</v>
       </c>
       <c r="E156">
-        <v>176.49000000000001</v>
+        <v>176.41999999999999</v>
       </c>
       <c r="F156">
-        <v>174.84</v>
+        <v>174.81999999999999</v>
       </c>
       <c r="G156">
         <v>158.53</v>
@@ -5864,23 +6569,23 @@
       <c r="A157">
         <v>49004</v>
       </c>
-      <c r="B157">
-        <v>2014</v>
-      </c>
-      <c r="C157">
-        <v>9</v>
-      </c>
-      <c r="D157">
-        <v>142.75</v>
+      <c r="B157" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" t="s">
+        <v>170</v>
+      </c>
+      <c r="D157" t="s">
+        <v>174</v>
       </c>
       <c r="E157">
-        <v>172.060000000000002</v>
+        <v>172.19999999999999</v>
       </c>
       <c r="F157">
-        <v>170.69</v>
+        <v>170.69999999999999</v>
       </c>
       <c r="G157">
-        <v>153.47</v>
+        <v>154.22999999999999</v>
       </c>
       <c r="H157">
         <v>0.38</v>
@@ -5889,7 +6594,7 @@
         <v>22.3</v>
       </c>
       <c r="J157">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K157">
         <v>0</v>
@@ -5899,23 +6604,23 @@
       <c r="A158">
         <v>49005</v>
       </c>
-      <c r="B158">
-        <v>2014</v>
-      </c>
-      <c r="C158">
-        <v>9</v>
-      </c>
-      <c r="D158">
-        <v>144.56</v>
+      <c r="B158" t="s">
+        <v>11</v>
+      </c>
+      <c r="C158" t="s">
+        <v>170</v>
+      </c>
+      <c r="D158" t="s">
+        <v>175</v>
       </c>
       <c r="E158">
-        <v>175.90000000000001</v>
+        <v>175.91999999999999</v>
       </c>
       <c r="F158">
-        <v>174.13999999999999</v>
+        <v>174.13</v>
       </c>
       <c r="G158">
-        <v>157.5</v>
+        <v>157.33000000000001</v>
       </c>
       <c r="H158">
         <v>0.37</v>
@@ -5924,7 +6629,7 @@
         <v>22.3</v>
       </c>
       <c r="J158">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K158">
         <v>0</v>
@@ -5934,17 +6639,17 @@
       <c r="A159">
         <v>49006</v>
       </c>
-      <c r="B159">
-        <v>2014</v>
-      </c>
-      <c r="C159">
-        <v>9</v>
-      </c>
-      <c r="D159">
-        <v>140.11000000000001</v>
+      <c r="B159" t="s">
+        <v>11</v>
+      </c>
+      <c r="C159" t="s">
+        <v>170</v>
+      </c>
+      <c r="D159" t="s">
+        <v>176</v>
       </c>
       <c r="E159">
-        <v>169.91999999999999</v>
+        <v>169.90000000000001</v>
       </c>
       <c r="F159">
         <v>168.40000000000001</v>
@@ -5969,29 +6674,29 @@
       <c r="A160">
         <v>49007</v>
       </c>
-      <c r="B160">
-        <v>2014</v>
-      </c>
-      <c r="C160">
-        <v>9</v>
-      </c>
-      <c r="D160">
-        <v>142.41999999999999</v>
+      <c r="B160" t="s">
+        <v>11</v>
+      </c>
+      <c r="C160" t="s">
+        <v>170</v>
+      </c>
+      <c r="D160" t="s">
+        <v>177</v>
       </c>
       <c r="E160">
-        <v>173.81</v>
+        <v>173.19</v>
       </c>
       <c r="F160">
-        <v>171.94</v>
+        <v>171.40000000000001</v>
       </c>
       <c r="G160">
-        <v>155.02000000000001</v>
+        <v>155.099999999999994</v>
       </c>
       <c r="H160">
         <v>0.39</v>
       </c>
       <c r="I160">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="J160">
         <v>36</v>
@@ -6004,17 +6709,17 @@
       <c r="A161">
         <v>49008</v>
       </c>
-      <c r="B161">
-        <v>2014</v>
-      </c>
-      <c r="C161">
-        <v>9</v>
-      </c>
-      <c r="D161">
-        <v>137.55000000000001</v>
+      <c r="B161" t="s">
+        <v>11</v>
+      </c>
+      <c r="C161" t="s">
+        <v>170</v>
+      </c>
+      <c r="D161" t="s">
+        <v>178</v>
       </c>
       <c r="E161">
-        <v>167.090000000000003</v>
+        <v>167.080000000000013</v>
       </c>
       <c r="F161">
         <v>165.34</v>
@@ -6039,26 +6744,26 @@
       <c r="A162">
         <v>49009</v>
       </c>
-      <c r="B162">
-        <v>2014</v>
-      </c>
-      <c r="C162">
-        <v>9</v>
-      </c>
-      <c r="D162">
-        <v>139.16999999999999</v>
+      <c r="B162" t="s">
+        <v>11</v>
+      </c>
+      <c r="C162" t="s">
+        <v>170</v>
+      </c>
+      <c r="D162" t="s">
+        <v>179</v>
       </c>
       <c r="E162">
-        <v>169.38999999999999</v>
+        <v>171.0</v>
       </c>
       <c r="F162">
-        <v>167.61000000000001</v>
+        <v>169.12</v>
       </c>
       <c r="G162">
-        <v>149.090000000000003</v>
+        <v>152.28</v>
       </c>
       <c r="H162">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="I162">
         <v>20.3</v>
@@ -6074,23 +6779,23 @@
       <c r="A163">
         <v>49010</v>
       </c>
-      <c r="B163">
-        <v>2014</v>
-      </c>
-      <c r="C163">
-        <v>9</v>
-      </c>
-      <c r="D163">
-        <v>140.77000000000001</v>
+      <c r="B163" t="s">
+        <v>11</v>
+      </c>
+      <c r="C163" t="s">
+        <v>170</v>
+      </c>
+      <c r="D163" t="s">
+        <v>180</v>
       </c>
       <c r="E163">
-        <v>168.99000000000001</v>
+        <v>168.84999999999999</v>
       </c>
       <c r="F163">
-        <v>167.74000000000001</v>
+        <v>167.59</v>
       </c>
       <c r="G163">
-        <v>138.59999999999999</v>
+        <v>138.18000000000001</v>
       </c>
       <c r="H163">
         <v>0.41</v>
@@ -6109,23 +6814,23 @@
       <c r="A164">
         <v>49011</v>
       </c>
-      <c r="B164">
-        <v>2014</v>
-      </c>
-      <c r="C164">
-        <v>9</v>
-      </c>
-      <c r="D164">
-        <v>138.46000000000001</v>
+      <c r="B164" t="s">
+        <v>11</v>
+      </c>
+      <c r="C164" t="s">
+        <v>170</v>
+      </c>
+      <c r="D164" t="s">
+        <v>181</v>
       </c>
       <c r="E164">
+        <v>167.53</v>
+      </c>
+      <c r="F164">
         <v>166.19999999999999</v>
       </c>
-      <c r="F164">
-        <v>165.039999999999992</v>
-      </c>
       <c r="G164">
-        <v>140.83000000000001</v>
+        <v>144.59</v>
       </c>
       <c r="H164">
         <v>0.39</v>
@@ -6144,23 +6849,23 @@
       <c r="A165">
         <v>49012</v>
       </c>
-      <c r="B165">
-        <v>2014</v>
-      </c>
-      <c r="C165">
-        <v>9</v>
-      </c>
-      <c r="D165">
-        <v>142.19</v>
+      <c r="B165" t="s">
+        <v>11</v>
+      </c>
+      <c r="C165" t="s">
+        <v>170</v>
+      </c>
+      <c r="D165" t="s">
+        <v>182</v>
       </c>
       <c r="E165">
-        <v>172.86000000000001</v>
+        <v>172.87</v>
       </c>
       <c r="F165">
-        <v>171.11000000000001</v>
+        <v>171.12</v>
       </c>
       <c r="G165">
-        <v>156.94</v>
+        <v>157.11000000000001</v>
       </c>
       <c r="H165">
         <v>0.37</v>
@@ -6179,23 +6884,23 @@
       <c r="A166">
         <v>49013</v>
       </c>
-      <c r="B166">
-        <v>2014</v>
-      </c>
-      <c r="C166">
-        <v>9</v>
-      </c>
-      <c r="D166">
-        <v>141.69</v>
+      <c r="B166" t="s">
+        <v>11</v>
+      </c>
+      <c r="C166" t="s">
+        <v>170</v>
+      </c>
+      <c r="D166" t="s">
+        <v>183</v>
       </c>
       <c r="E166">
-        <v>169.84999999999999</v>
+        <v>169.94</v>
       </c>
       <c r="F166">
-        <v>168.53999999999999</v>
+        <v>168.61000000000001</v>
       </c>
       <c r="G166">
-        <v>145.63</v>
+        <v>147.66999999999999</v>
       </c>
       <c r="H166">
         <v>0.4</v>
@@ -6214,23 +6919,23 @@
       <c r="A167">
         <v>49014</v>
       </c>
-      <c r="B167">
-        <v>2014</v>
-      </c>
-      <c r="C167">
-        <v>9</v>
-      </c>
-      <c r="D167">
-        <v>139.13999999999999</v>
+      <c r="B167" t="s">
+        <v>11</v>
+      </c>
+      <c r="C167" t="s">
+        <v>170</v>
+      </c>
+      <c r="D167" t="s">
+        <v>184</v>
       </c>
       <c r="E167">
-        <v>166.13</v>
+        <v>166.12</v>
       </c>
       <c r="F167">
-        <v>164.90000000000001</v>
+        <v>164.87</v>
       </c>
       <c r="G167">
-        <v>143.24000000000001</v>
+        <v>142.88</v>
       </c>
       <c r="H167">
         <v>0.41</v>
@@ -6249,29 +6954,29 @@
       <c r="A168">
         <v>49017</v>
       </c>
-      <c r="B168">
-        <v>2014</v>
-      </c>
-      <c r="C168">
-        <v>9</v>
-      </c>
-      <c r="D168">
-        <v>141.41999999999999</v>
+      <c r="B168" t="s">
+        <v>11</v>
+      </c>
+      <c r="C168" t="s">
+        <v>170</v>
+      </c>
+      <c r="D168" t="s">
+        <v>185</v>
       </c>
       <c r="E168">
-        <v>172.58000000000001</v>
+        <v>167.69999999999999</v>
       </c>
       <c r="F168">
-        <v>170.69999999999999</v>
+        <v>166.13999999999999</v>
       </c>
       <c r="G168">
-        <v>153.27000000000001</v>
+        <v>144.58000000000001</v>
       </c>
       <c r="H168">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I168">
-        <v>21.3</v>
+        <v>20.1</v>
       </c>
       <c r="J168">
         <v>36</v>
@@ -6284,29 +6989,29 @@
       <c r="A169">
         <v>49018</v>
       </c>
-      <c r="B169">
-        <v>2014</v>
-      </c>
-      <c r="C169">
-        <v>9</v>
-      </c>
-      <c r="D169">
-        <v>145.69</v>
+      <c r="B169" t="s">
+        <v>11</v>
+      </c>
+      <c r="C169" t="s">
+        <v>170</v>
+      </c>
+      <c r="D169" t="s">
+        <v>186</v>
       </c>
       <c r="E169">
-        <v>178.84999999999999</v>
+        <v>176.99000000000001</v>
       </c>
       <c r="F169">
-        <v>176.88</v>
+        <v>175.099999999999994</v>
       </c>
       <c r="G169">
-        <v>164.97999999999999</v>
+        <v>161.72</v>
       </c>
       <c r="H169">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="I169">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="J169">
         <v>36</v>
@@ -6319,23 +7024,23 @@
       <c r="A170">
         <v>49019</v>
       </c>
-      <c r="B170">
-        <v>2014</v>
-      </c>
-      <c r="C170">
-        <v>9</v>
-      </c>
-      <c r="D170">
-        <v>138.56</v>
+      <c r="B170" t="s">
+        <v>11</v>
+      </c>
+      <c r="C170" t="s">
+        <v>170</v>
+      </c>
+      <c r="D170" t="s">
+        <v>187</v>
       </c>
       <c r="E170">
-        <v>167.49000000000001</v>
+        <v>170.71000000000001</v>
       </c>
       <c r="F170">
-        <v>166.25999999999999</v>
+        <v>169.28999999999999</v>
       </c>
       <c r="G170">
-        <v>136.97</v>
+        <v>144.44</v>
       </c>
       <c r="H170">
         <v>0.4</v>
@@ -6344,7 +7049,7 @@
         <v>20.3</v>
       </c>
       <c r="J170">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K170">
         <v>0</v>
@@ -6354,23 +7059,23 @@
       <c r="A171">
         <v>49020</v>
       </c>
-      <c r="B171">
-        <v>2014</v>
-      </c>
-      <c r="C171">
-        <v>9</v>
-      </c>
-      <c r="D171">
-        <v>145.31</v>
+      <c r="B171" t="s">
+        <v>11</v>
+      </c>
+      <c r="C171" t="s">
+        <v>170</v>
+      </c>
+      <c r="D171" t="s">
+        <v>188</v>
       </c>
       <c r="E171">
-        <v>177.62</v>
+        <v>177.61000000000001</v>
       </c>
       <c r="F171">
-        <v>175.71000000000001</v>
+        <v>175.69999999999999</v>
       </c>
       <c r="G171">
-        <v>160.19999999999999</v>
+        <v>159.99000000000001</v>
       </c>
       <c r="H171">
         <v>0.38</v>
@@ -6389,32 +7094,32 @@
       <c r="A172">
         <v>49021</v>
       </c>
-      <c r="B172">
-        <v>2014</v>
-      </c>
-      <c r="C172">
-        <v>9</v>
-      </c>
-      <c r="D172">
-        <v>134.84999999999999</v>
+      <c r="B172" t="s">
+        <v>11</v>
+      </c>
+      <c r="C172" t="s">
+        <v>170</v>
+      </c>
+      <c r="D172" t="s">
+        <v>189</v>
       </c>
       <c r="E172">
-        <v>160.21000000000001</v>
+        <v>171.47</v>
       </c>
       <c r="F172">
-        <v>159.31999999999999</v>
+        <v>170.050000000000011</v>
       </c>
       <c r="G172">
-        <v>127.73</v>
+        <v>151.56999999999999</v>
       </c>
       <c r="H172">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="I172">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="J172">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K172">
         <v>0</v>
@@ -6424,23 +7129,23 @@
       <c r="A173">
         <v>49001</v>
       </c>
-      <c r="B173">
-        <v>2014</v>
-      </c>
-      <c r="C173">
-        <v>10</v>
-      </c>
-      <c r="D173">
-        <v>106.28</v>
+      <c r="B173" t="s">
+        <v>11</v>
+      </c>
+      <c r="C173" t="s">
+        <v>190</v>
+      </c>
+      <c r="D173" t="s">
+        <v>191</v>
       </c>
       <c r="E173">
-        <v>154.5</v>
+        <v>154.52000000000001</v>
       </c>
       <c r="F173">
-        <v>149.41999999999999</v>
+        <v>149.41</v>
       </c>
       <c r="G173">
-        <v>136.0099999999999909</v>
+        <v>136.0</v>
       </c>
       <c r="H173">
         <v>0.42</v>
@@ -6459,32 +7164,32 @@
       <c r="A174">
         <v>49002</v>
       </c>
-      <c r="B174">
-        <v>2014</v>
-      </c>
-      <c r="C174">
-        <v>10</v>
-      </c>
-      <c r="D174">
-        <v>110.069999999999993</v>
+      <c r="B174" t="s">
+        <v>11</v>
+      </c>
+      <c r="C174" t="s">
+        <v>190</v>
+      </c>
+      <c r="D174" t="s">
+        <v>192</v>
       </c>
       <c r="E174">
-        <v>162.84999999999999</v>
+        <v>153.58000000000001</v>
       </c>
       <c r="F174">
-        <v>156.55000000000001</v>
+        <v>148.18000000000001</v>
       </c>
       <c r="G174">
-        <v>147.97</v>
+        <v>136.59</v>
       </c>
       <c r="H174">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="I174">
         <v>18.7</v>
       </c>
       <c r="J174">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K174">
         <v>0</v>
@@ -6494,23 +7199,23 @@
       <c r="A175">
         <v>49003</v>
       </c>
-      <c r="B175">
-        <v>2014</v>
-      </c>
-      <c r="C175">
-        <v>10</v>
-      </c>
-      <c r="D175">
-        <v>105.92</v>
+      <c r="B175" t="s">
+        <v>11</v>
+      </c>
+      <c r="C175" t="s">
+        <v>190</v>
+      </c>
+      <c r="D175" t="s">
+        <v>193</v>
       </c>
       <c r="E175">
-        <v>154.81</v>
+        <v>153.44</v>
       </c>
       <c r="F175">
-        <v>149.34</v>
+        <v>148.41999999999999</v>
       </c>
       <c r="G175">
-        <v>139.41</v>
+        <v>135.74000000000001</v>
       </c>
       <c r="H175">
         <v>0.4</v>
@@ -6529,23 +7234,23 @@
       <c r="A176">
         <v>49004</v>
       </c>
-      <c r="B176">
-        <v>2014</v>
-      </c>
-      <c r="C176">
-        <v>10</v>
-      </c>
-      <c r="D176">
-        <v>103.65000000000001</v>
+      <c r="B176" t="s">
+        <v>11</v>
+      </c>
+      <c r="C176" t="s">
+        <v>190</v>
+      </c>
+      <c r="D176" t="s">
+        <v>194</v>
       </c>
       <c r="E176">
-        <v>148.66</v>
+        <v>151.52000000000001</v>
       </c>
       <c r="F176">
-        <v>144.53</v>
+        <v>146.5</v>
       </c>
       <c r="G176">
-        <v>129.81999999999999</v>
+        <v>134.56999999999999</v>
       </c>
       <c r="H176">
         <v>0.41</v>
@@ -6554,7 +7259,7 @@
         <v>20.6</v>
       </c>
       <c r="J176">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K176">
         <v>0</v>
@@ -6564,23 +7269,23 @@
       <c r="A177">
         <v>49005</v>
       </c>
-      <c r="B177">
-        <v>2014</v>
-      </c>
-      <c r="C177">
-        <v>10</v>
-      </c>
-      <c r="D177">
-        <v>107.040000000000006</v>
+      <c r="B177" t="s">
+        <v>11</v>
+      </c>
+      <c r="C177" t="s">
+        <v>190</v>
+      </c>
+      <c r="D177" t="s">
+        <v>195</v>
       </c>
       <c r="E177">
-        <v>156.53</v>
+        <v>157.49000000000001</v>
       </c>
       <c r="F177">
-        <v>151.039999999999992</v>
+        <v>151.80000000000001</v>
       </c>
       <c r="G177">
-        <v>138.78</v>
+        <v>141.81</v>
       </c>
       <c r="H177">
         <v>0.38</v>
@@ -6589,7 +7294,7 @@
         <v>20.4</v>
       </c>
       <c r="J177">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K177">
         <v>0</v>
@@ -6599,23 +7304,23 @@
       <c r="A178">
         <v>49006</v>
       </c>
-      <c r="B178">
-        <v>2014</v>
-      </c>
-      <c r="C178">
-        <v>10</v>
-      </c>
-      <c r="D178">
-        <v>95.93000000000001</v>
+      <c r="B178" t="s">
+        <v>11</v>
+      </c>
+      <c r="C178" t="s">
+        <v>190</v>
+      </c>
+      <c r="D178" t="s">
+        <v>196</v>
       </c>
       <c r="E178">
-        <v>134.61000000000001</v>
+        <v>133.83000000000001</v>
       </c>
       <c r="F178">
-        <v>131.02000000000001</v>
+        <v>130.34999999999999</v>
       </c>
       <c r="G178">
-        <v>112.2</v>
+        <v>109.94</v>
       </c>
       <c r="H178">
         <v>0.48</v>
@@ -6634,29 +7339,29 @@
       <c r="A179">
         <v>49007</v>
       </c>
-      <c r="B179">
-        <v>2014</v>
-      </c>
-      <c r="C179">
-        <v>10</v>
-      </c>
-      <c r="D179">
-        <v>105.90000000000001</v>
+      <c r="B179" t="s">
+        <v>11</v>
+      </c>
+      <c r="C179" t="s">
+        <v>190</v>
+      </c>
+      <c r="D179" t="s">
+        <v>197</v>
       </c>
       <c r="E179">
-        <v>155.94</v>
+        <v>157.40000000000001</v>
       </c>
       <c r="F179">
-        <v>150.34999999999999</v>
+        <v>151.69999999999999</v>
       </c>
       <c r="G179">
-        <v>140.44999999999999</v>
+        <v>142.25999999999999</v>
       </c>
       <c r="H179">
         <v>0.4</v>
       </c>
       <c r="I179">
-        <v>17.9</v>
+        <v>18.3</v>
       </c>
       <c r="J179">
         <v>36</v>
@@ -6669,14 +7374,14 @@
       <c r="A180">
         <v>49008</v>
       </c>
-      <c r="B180">
-        <v>2014</v>
-      </c>
-      <c r="C180">
-        <v>10</v>
-      </c>
-      <c r="D180">
-        <v>100.19</v>
+      <c r="B180" t="s">
+        <v>11</v>
+      </c>
+      <c r="C180" t="s">
+        <v>190</v>
+      </c>
+      <c r="D180" t="s">
+        <v>198</v>
       </c>
       <c r="E180">
         <v>146.88999999999999</v>
@@ -6685,7 +7390,7 @@
         <v>141.63</v>
       </c>
       <c r="G180">
-        <v>131.94</v>
+        <v>131.93000000000001</v>
       </c>
       <c r="H180">
         <v>0.42</v>
@@ -6704,26 +7409,26 @@
       <c r="A181">
         <v>49009</v>
       </c>
-      <c r="B181">
-        <v>2014</v>
-      </c>
-      <c r="C181">
-        <v>10</v>
-      </c>
-      <c r="D181">
-        <v>101.84</v>
+      <c r="B181" t="s">
+        <v>11</v>
+      </c>
+      <c r="C181" t="s">
+        <v>190</v>
+      </c>
+      <c r="D181" t="s">
+        <v>199</v>
       </c>
       <c r="E181">
-        <v>150.13999999999999</v>
+        <v>151.94999999999999</v>
       </c>
       <c r="F181">
-        <v>144.77000000000001</v>
+        <v>146.52000000000001</v>
       </c>
       <c r="G181">
-        <v>136.47</v>
+        <v>138.49000000000001</v>
       </c>
       <c r="H181">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="I181">
         <v>17.6</v>
@@ -6739,23 +7444,23 @@
       <c r="A182">
         <v>49010</v>
       </c>
-      <c r="B182">
-        <v>2014</v>
-      </c>
-      <c r="C182">
-        <v>10</v>
-      </c>
-      <c r="D182">
-        <v>97.45</v>
+      <c r="B182" t="s">
+        <v>11</v>
+      </c>
+      <c r="C182" t="s">
+        <v>190</v>
+      </c>
+      <c r="D182" t="s">
+        <v>200</v>
       </c>
       <c r="E182">
-        <v>136.21000000000001</v>
+        <v>136.0099999999999909</v>
       </c>
       <c r="F182">
-        <v>132.93000000000001</v>
+        <v>132.72</v>
       </c>
       <c r="G182">
-        <v>111.16</v>
+        <v>110.59999999999999</v>
       </c>
       <c r="H182">
         <v>0.45</v>
@@ -6774,23 +7479,23 @@
       <c r="A183">
         <v>49011</v>
       </c>
-      <c r="B183">
-        <v>2014</v>
-      </c>
-      <c r="C183">
-        <v>10</v>
-      </c>
-      <c r="D183">
-        <v>97.019999999999996</v>
+      <c r="B183" t="s">
+        <v>11</v>
+      </c>
+      <c r="C183" t="s">
+        <v>190</v>
+      </c>
+      <c r="D183" t="s">
+        <v>201</v>
       </c>
       <c r="E183">
-        <v>136.49000000000001</v>
+        <v>138.40000000000001</v>
       </c>
       <c r="F183">
-        <v>133.25999999999999</v>
+        <v>134.55000000000001</v>
       </c>
       <c r="G183">
-        <v>114.29000000000001</v>
+        <v>116.62</v>
       </c>
       <c r="H183">
         <v>0.43</v>
@@ -6809,23 +7514,23 @@
       <c r="A184">
         <v>49012</v>
       </c>
-      <c r="B184">
-        <v>2014</v>
-      </c>
-      <c r="C184">
-        <v>10</v>
-      </c>
-      <c r="D184">
-        <v>105.13</v>
+      <c r="B184" t="s">
+        <v>11</v>
+      </c>
+      <c r="C184" t="s">
+        <v>190</v>
+      </c>
+      <c r="D184" t="s">
+        <v>202</v>
       </c>
       <c r="E184">
         <v>154.72999999999999</v>
       </c>
       <c r="F184">
-        <v>149.099999999999994</v>
+        <v>149.090000000000003</v>
       </c>
       <c r="G184">
-        <v>140.38999999999999</v>
+        <v>140.28999999999999</v>
       </c>
       <c r="H184">
         <v>0.39</v>
@@ -6844,26 +7549,26 @@
       <c r="A185">
         <v>49013</v>
       </c>
-      <c r="B185">
-        <v>2014</v>
-      </c>
-      <c r="C185">
-        <v>10</v>
-      </c>
-      <c r="D185">
-        <v>98.81</v>
+      <c r="B185" t="s">
+        <v>11</v>
+      </c>
+      <c r="C185" t="s">
+        <v>190</v>
+      </c>
+      <c r="D185" t="s">
+        <v>203</v>
       </c>
       <c r="E185">
-        <v>140.080000000000013</v>
+        <v>140.41999999999999</v>
       </c>
       <c r="F185">
-        <v>136.080000000000013</v>
+        <v>136.30000000000001</v>
       </c>
       <c r="G185">
-        <v>118.31</v>
+        <v>119.049999999999997</v>
       </c>
       <c r="H185">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I185">
         <v>20.6</v>
@@ -6879,20 +7584,20 @@
       <c r="A186">
         <v>49014</v>
       </c>
-      <c r="B186">
-        <v>2014</v>
-      </c>
-      <c r="C186">
-        <v>10</v>
-      </c>
-      <c r="D186">
-        <v>94.12</v>
+      <c r="B186" t="s">
+        <v>11</v>
+      </c>
+      <c r="C186" t="s">
+        <v>190</v>
+      </c>
+      <c r="D186" t="s">
+        <v>204</v>
       </c>
       <c r="E186">
-        <v>133.71000000000001</v>
+        <v>133.80000000000001</v>
       </c>
       <c r="F186">
-        <v>129.78</v>
+        <v>129.81</v>
       </c>
       <c r="G186">
         <v>115.45</v>
@@ -6914,29 +7619,29 @@
       <c r="A187">
         <v>49017</v>
       </c>
-      <c r="B187">
-        <v>2014</v>
-      </c>
-      <c r="C187">
-        <v>10</v>
-      </c>
-      <c r="D187">
-        <v>104.92</v>
+      <c r="B187" t="s">
+        <v>11</v>
+      </c>
+      <c r="C187" t="s">
+        <v>190</v>
+      </c>
+      <c r="D187" t="s">
+        <v>205</v>
       </c>
       <c r="E187">
-        <v>154.18000000000001</v>
+        <v>149.53</v>
       </c>
       <c r="F187">
-        <v>148.68000000000001</v>
+        <v>144.78</v>
       </c>
       <c r="G187">
-        <v>138.69</v>
+        <v>132.34</v>
       </c>
       <c r="H187">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="I187">
-        <v>19.1</v>
+        <v>17.4</v>
       </c>
       <c r="J187">
         <v>36</v>
@@ -6949,29 +7654,29 @@
       <c r="A188">
         <v>49018</v>
       </c>
-      <c r="B188">
-        <v>2014</v>
-      </c>
-      <c r="C188">
-        <v>10</v>
-      </c>
-      <c r="D188">
-        <v>105.87</v>
+      <c r="B188" t="s">
+        <v>11</v>
+      </c>
+      <c r="C188" t="s">
+        <v>190</v>
+      </c>
+      <c r="D188" t="s">
+        <v>206</v>
       </c>
       <c r="E188">
-        <v>155.0</v>
+        <v>152.19999999999999</v>
       </c>
       <c r="F188">
-        <v>149.66999999999999</v>
+        <v>146.99000000000001</v>
       </c>
       <c r="G188">
-        <v>139.50999999999999</v>
+        <v>136.94999999999999</v>
       </c>
       <c r="H188">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="I188">
-        <v>18.8</v>
+        <v>19.3</v>
       </c>
       <c r="J188">
         <v>36</v>
@@ -6984,32 +7689,32 @@
       <c r="A189">
         <v>49019</v>
       </c>
-      <c r="B189">
-        <v>2014</v>
-      </c>
-      <c r="C189">
-        <v>10</v>
-      </c>
-      <c r="D189">
-        <v>92.95</v>
+      <c r="B189" t="s">
+        <v>11</v>
+      </c>
+      <c r="C189" t="s">
+        <v>190</v>
+      </c>
+      <c r="D189" t="s">
+        <v>207</v>
       </c>
       <c r="E189">
-        <v>127.56999999999999</v>
+        <v>134.59</v>
       </c>
       <c r="F189">
-        <v>125.019999999999996</v>
+        <v>131.38</v>
       </c>
       <c r="G189">
-        <v>96.70999999999999</v>
+        <v>109.84</v>
       </c>
       <c r="H189">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="I189">
         <v>17.9</v>
       </c>
       <c r="J189">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K189">
         <v>0</v>
@@ -7019,23 +7724,23 @@
       <c r="A190">
         <v>49020</v>
       </c>
-      <c r="B190">
-        <v>2014</v>
-      </c>
-      <c r="C190">
-        <v>10</v>
-      </c>
-      <c r="D190">
-        <v>103.45</v>
+      <c r="B190" t="s">
+        <v>11</v>
+      </c>
+      <c r="C190" t="s">
+        <v>190</v>
+      </c>
+      <c r="D190" t="s">
+        <v>208</v>
       </c>
       <c r="E190">
-        <v>150.40000000000001</v>
+        <v>150.38</v>
       </c>
       <c r="F190">
-        <v>145.25</v>
+        <v>145.24000000000001</v>
       </c>
       <c r="G190">
-        <v>133.080000000000013</v>
+        <v>133.0099999999999909</v>
       </c>
       <c r="H190">
         <v>0.43</v>
@@ -7054,32 +7759,32 @@
       <c r="A191">
         <v>49021</v>
       </c>
-      <c r="B191">
-        <v>2014</v>
-      </c>
-      <c r="C191">
-        <v>10</v>
-      </c>
-      <c r="D191">
-        <v>90.28</v>
+      <c r="B191" t="s">
+        <v>11</v>
+      </c>
+      <c r="C191" t="s">
+        <v>190</v>
+      </c>
+      <c r="D191" t="s">
+        <v>209</v>
       </c>
       <c r="E191">
-        <v>123.89</v>
+        <v>143.84999999999999</v>
       </c>
       <c r="F191">
-        <v>121.56</v>
+        <v>139.84999999999999</v>
       </c>
       <c r="G191">
-        <v>98.29000000000001</v>
+        <v>123.94</v>
       </c>
       <c r="H191">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="I191">
-        <v>19.9</v>
+        <v>20.4</v>
       </c>
       <c r="J191">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K191">
         <v>0</v>
@@ -7089,23 +7794,23 @@
       <c r="A192">
         <v>49001</v>
       </c>
-      <c r="B192">
-        <v>2014</v>
-      </c>
-      <c r="C192">
-        <v>11</v>
-      </c>
-      <c r="D192">
-        <v>49.14</v>
+      <c r="B192" t="s">
+        <v>11</v>
+      </c>
+      <c r="C192" t="s">
+        <v>210</v>
+      </c>
+      <c r="D192" t="s">
+        <v>211</v>
       </c>
       <c r="E192">
-        <v>75.59999999999999</v>
+        <v>75.62</v>
       </c>
       <c r="F192">
-        <v>72.53</v>
+        <v>72.52</v>
       </c>
       <c r="G192">
-        <v>59.52</v>
+        <v>59.51</v>
       </c>
       <c r="H192">
         <v>0.58</v>
@@ -7124,32 +7829,32 @@
       <c r="A193">
         <v>49002</v>
       </c>
-      <c r="B193">
-        <v>2014</v>
-      </c>
-      <c r="C193">
-        <v>11</v>
-      </c>
-      <c r="D193">
-        <v>51.47</v>
+      <c r="B193" t="s">
+        <v>11</v>
+      </c>
+      <c r="C193" t="s">
+        <v>210</v>
+      </c>
+      <c r="D193" t="s">
+        <v>212</v>
       </c>
       <c r="E193">
-        <v>79.099999999999994</v>
+        <v>75.58</v>
       </c>
       <c r="F193">
-        <v>75.48</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="G193">
-        <v>61.72</v>
+        <v>58.28</v>
       </c>
       <c r="H193">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="I193">
         <v>15.4</v>
       </c>
       <c r="J193">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K193">
         <v>0</v>
@@ -7159,26 +7864,26 @@
       <c r="A194">
         <v>49003</v>
       </c>
-      <c r="B194">
-        <v>2014</v>
-      </c>
-      <c r="C194">
-        <v>11</v>
-      </c>
-      <c r="D194">
-        <v>50.54</v>
+      <c r="B194" t="s">
+        <v>11</v>
+      </c>
+      <c r="C194" t="s">
+        <v>210</v>
+      </c>
+      <c r="D194" t="s">
+        <v>213</v>
       </c>
       <c r="E194">
-        <v>76.27</v>
+        <v>74.5</v>
       </c>
       <c r="F194">
-        <v>73.14</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="G194">
-        <v>58.71</v>
+        <v>55.78</v>
       </c>
       <c r="H194">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="I194">
         <v>17.5</v>
@@ -7194,32 +7899,32 @@
       <c r="A195">
         <v>49004</v>
       </c>
-      <c r="B195">
-        <v>2014</v>
-      </c>
-      <c r="C195">
-        <v>11</v>
-      </c>
-      <c r="D195">
-        <v>46.84</v>
+      <c r="B195" t="s">
+        <v>11</v>
+      </c>
+      <c r="C195" t="s">
+        <v>210</v>
+      </c>
+      <c r="D195" t="s">
+        <v>214</v>
       </c>
       <c r="E195">
-        <v>65.31</v>
+        <v>69.89</v>
       </c>
       <c r="F195">
-        <v>63.56</v>
+        <v>67.39</v>
       </c>
       <c r="G195">
-        <v>43.54</v>
+        <v>51.56</v>
       </c>
       <c r="H195">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="I195">
         <v>17.5</v>
       </c>
       <c r="J195">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K195">
         <v>0</v>
@@ -7229,32 +7934,32 @@
       <c r="A196">
         <v>49005</v>
       </c>
-      <c r="B196">
-        <v>2014</v>
-      </c>
-      <c r="C196">
-        <v>11</v>
-      </c>
-      <c r="D196">
-        <v>50.58</v>
+      <c r="B196" t="s">
+        <v>11</v>
+      </c>
+      <c r="C196" t="s">
+        <v>210</v>
+      </c>
+      <c r="D196" t="s">
+        <v>215</v>
       </c>
       <c r="E196">
-        <v>77.77</v>
+        <v>78.66</v>
       </c>
       <c r="F196">
-        <v>74.44</v>
+        <v>75.16</v>
       </c>
       <c r="G196">
-        <v>60.92</v>
+        <v>62.54</v>
       </c>
       <c r="H196">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="I196">
         <v>17.3</v>
       </c>
       <c r="J196">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K196">
         <v>0</v>
@@ -7264,17 +7969,17 @@
       <c r="A197">
         <v>49006</v>
       </c>
-      <c r="B197">
-        <v>2014</v>
-      </c>
-      <c r="C197">
-        <v>11</v>
-      </c>
-      <c r="D197">
-        <v>46.94</v>
+      <c r="B197" t="s">
+        <v>11</v>
+      </c>
+      <c r="C197" t="s">
+        <v>210</v>
+      </c>
+      <c r="D197" t="s">
+        <v>216</v>
       </c>
       <c r="E197">
-        <v>69.79000000000001</v>
+        <v>69.75</v>
       </c>
       <c r="F197">
         <v>67.43000000000001</v>
@@ -7299,29 +8004,29 @@
       <c r="A198">
         <v>49007</v>
       </c>
-      <c r="B198">
-        <v>2014</v>
-      </c>
-      <c r="C198">
-        <v>11</v>
-      </c>
-      <c r="D198">
-        <v>51.07</v>
+      <c r="B198" t="s">
+        <v>11</v>
+      </c>
+      <c r="C198" t="s">
+        <v>210</v>
+      </c>
+      <c r="D198" t="s">
+        <v>217</v>
       </c>
       <c r="E198">
-        <v>80.31999999999999</v>
+        <v>80.78</v>
       </c>
       <c r="F198">
-        <v>76.70999999999999</v>
+        <v>77.049999999999997</v>
       </c>
       <c r="G198">
-        <v>64.69</v>
+        <v>65.84</v>
       </c>
       <c r="H198">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="I198">
-        <v>14.6</v>
+        <v>15.0</v>
       </c>
       <c r="J198">
         <v>36</v>
@@ -7334,14 +8039,14 @@
       <c r="A199">
         <v>49008</v>
       </c>
-      <c r="B199">
-        <v>2014</v>
-      </c>
-      <c r="C199">
-        <v>11</v>
-      </c>
-      <c r="D199">
-        <v>47.56</v>
+      <c r="B199" t="s">
+        <v>11</v>
+      </c>
+      <c r="C199" t="s">
+        <v>210</v>
+      </c>
+      <c r="D199" t="s">
+        <v>218</v>
       </c>
       <c r="E199">
         <v>73.26000000000001</v>
@@ -7369,26 +8074,26 @@
       <c r="A200">
         <v>49009</v>
       </c>
-      <c r="B200">
-        <v>2014</v>
-      </c>
-      <c r="C200">
-        <v>11</v>
-      </c>
-      <c r="D200">
-        <v>46.57</v>
+      <c r="B200" t="s">
+        <v>11</v>
+      </c>
+      <c r="C200" t="s">
+        <v>210</v>
+      </c>
+      <c r="D200" t="s">
+        <v>219</v>
       </c>
       <c r="E200">
-        <v>72.19</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="F200">
-        <v>69.069999999999993</v>
+        <v>69.3</v>
       </c>
       <c r="G200">
-        <v>57.41</v>
+        <v>59.030000000000001</v>
       </c>
       <c r="H200">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="I200">
         <v>14.2</v>
@@ -7404,23 +8109,23 @@
       <c r="A201">
         <v>49010</v>
       </c>
-      <c r="B201">
-        <v>2014</v>
-      </c>
-      <c r="C201">
-        <v>11</v>
-      </c>
-      <c r="D201">
-        <v>46.76</v>
+      <c r="B201" t="s">
+        <v>11</v>
+      </c>
+      <c r="C201" t="s">
+        <v>210</v>
+      </c>
+      <c r="D201" t="s">
+        <v>220</v>
       </c>
       <c r="E201">
-        <v>66.069999999999993</v>
+        <v>65.78</v>
       </c>
       <c r="F201">
-        <v>64.31</v>
+        <v>64.049999999999997</v>
       </c>
       <c r="G201">
-        <v>45.1</v>
+        <v>44.68</v>
       </c>
       <c r="H201">
         <v>0.63</v>
@@ -7439,26 +8144,26 @@
       <c r="A202">
         <v>49011</v>
       </c>
-      <c r="B202">
-        <v>2014</v>
-      </c>
-      <c r="C202">
-        <v>11</v>
-      </c>
-      <c r="D202">
-        <v>43.59</v>
+      <c r="B202" t="s">
+        <v>11</v>
+      </c>
+      <c r="C202" t="s">
+        <v>210</v>
+      </c>
+      <c r="D202" t="s">
+        <v>221</v>
       </c>
       <c r="E202">
-        <v>59.28</v>
+        <v>60.98</v>
       </c>
       <c r="F202">
-        <v>57.97</v>
+        <v>59.35</v>
       </c>
       <c r="G202">
-        <v>37.26</v>
+        <v>39.7</v>
       </c>
       <c r="H202">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="I202">
         <v>16.8</v>
@@ -7474,23 +8179,23 @@
       <c r="A203">
         <v>49012</v>
       </c>
-      <c r="B203">
-        <v>2014</v>
-      </c>
-      <c r="C203">
-        <v>11</v>
-      </c>
-      <c r="D203">
-        <v>48.49</v>
+      <c r="B203" t="s">
+        <v>11</v>
+      </c>
+      <c r="C203" t="s">
+        <v>210</v>
+      </c>
+      <c r="D203" t="s">
+        <v>222</v>
       </c>
       <c r="E203">
-        <v>72.98999999999999</v>
+        <v>73.0</v>
       </c>
       <c r="F203">
-        <v>69.97</v>
+        <v>69.98</v>
       </c>
       <c r="G203">
-        <v>56.29</v>
+        <v>56.31</v>
       </c>
       <c r="H203">
         <v>0.58</v>
@@ -7509,23 +8214,23 @@
       <c r="A204">
         <v>49013</v>
       </c>
-      <c r="B204">
-        <v>2014</v>
-      </c>
-      <c r="C204">
-        <v>11</v>
-      </c>
-      <c r="D204">
-        <v>45.16</v>
+      <c r="B204" t="s">
+        <v>11</v>
+      </c>
+      <c r="C204" t="s">
+        <v>210</v>
+      </c>
+      <c r="D204" t="s">
+        <v>223</v>
       </c>
       <c r="E204">
-        <v>63.45</v>
+        <v>64.36</v>
       </c>
       <c r="F204">
-        <v>61.57</v>
+        <v>62.34</v>
       </c>
       <c r="G204">
-        <v>43.92</v>
+        <v>45.48</v>
       </c>
       <c r="H204">
         <v>0.65</v>
@@ -7544,23 +8249,23 @@
       <c r="A205">
         <v>49014</v>
       </c>
-      <c r="B205">
-        <v>2014</v>
-      </c>
-      <c r="C205">
-        <v>11</v>
-      </c>
-      <c r="D205">
-        <v>45.34</v>
+      <c r="B205" t="s">
+        <v>11</v>
+      </c>
+      <c r="C205" t="s">
+        <v>210</v>
+      </c>
+      <c r="D205" t="s">
+        <v>224</v>
       </c>
       <c r="E205">
-        <v>64.42</v>
+        <v>64.45</v>
       </c>
       <c r="F205">
-        <v>62.4</v>
+        <v>62.39</v>
       </c>
       <c r="G205">
-        <v>45.65</v>
+        <v>45.64</v>
       </c>
       <c r="H205">
         <v>0.65</v>
@@ -7579,29 +8284,29 @@
       <c r="A206">
         <v>49017</v>
       </c>
-      <c r="B206">
-        <v>2014</v>
-      </c>
-      <c r="C206">
-        <v>11</v>
-      </c>
-      <c r="D206">
-        <v>49.98</v>
+      <c r="B206" t="s">
+        <v>11</v>
+      </c>
+      <c r="C206" t="s">
+        <v>210</v>
+      </c>
+      <c r="D206" t="s">
+        <v>225</v>
       </c>
       <c r="E206">
-        <v>77.67</v>
+        <v>75.48</v>
       </c>
       <c r="F206">
-        <v>74.26000000000001</v>
+        <v>72.56</v>
       </c>
       <c r="G206">
-        <v>61.16</v>
+        <v>58.58</v>
       </c>
       <c r="H206">
-        <v>0.56</v>
+        <v>0.57</v>
       </c>
       <c r="I206">
-        <v>15.8</v>
+        <v>14.1</v>
       </c>
       <c r="J206">
         <v>36</v>
@@ -7614,29 +8319,29 @@
       <c r="A207">
         <v>49018</v>
       </c>
-      <c r="B207">
-        <v>2014</v>
-      </c>
-      <c r="C207">
-        <v>11</v>
-      </c>
-      <c r="D207">
-        <v>49.24</v>
+      <c r="B207" t="s">
+        <v>11</v>
+      </c>
+      <c r="C207" t="s">
+        <v>210</v>
+      </c>
+      <c r="D207" t="s">
+        <v>226</v>
       </c>
       <c r="E207">
-        <v>77.29000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="F207">
-        <v>73.90000000000001</v>
+        <v>71.47</v>
       </c>
       <c r="G207">
-        <v>63.13</v>
+        <v>58.99</v>
       </c>
       <c r="H207">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="I207">
-        <v>15.5</v>
+        <v>16.1</v>
       </c>
       <c r="J207">
         <v>36</v>
@@ -7649,32 +8354,32 @@
       <c r="A208">
         <v>49019</v>
       </c>
-      <c r="B208">
-        <v>2014</v>
-      </c>
-      <c r="C208">
-        <v>11</v>
-      </c>
-      <c r="D208">
-        <v>44.96</v>
+      <c r="B208" t="s">
+        <v>11</v>
+      </c>
+      <c r="C208" t="s">
+        <v>210</v>
+      </c>
+      <c r="D208" t="s">
+        <v>227</v>
       </c>
       <c r="E208">
-        <v>62.83</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="F208">
-        <v>61.41</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G208">
-        <v>41.64</v>
+        <v>47.34</v>
       </c>
       <c r="H208">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="I208">
         <v>14.6</v>
       </c>
       <c r="J208">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K208">
         <v>0</v>
@@ -7684,23 +8389,23 @@
       <c r="A209">
         <v>49020</v>
       </c>
-      <c r="B209">
-        <v>2014</v>
-      </c>
-      <c r="C209">
-        <v>11</v>
-      </c>
-      <c r="D209">
-        <v>48.82</v>
+      <c r="B209" t="s">
+        <v>11</v>
+      </c>
+      <c r="C209" t="s">
+        <v>210</v>
+      </c>
+      <c r="D209" t="s">
+        <v>228</v>
       </c>
       <c r="E209">
-        <v>73.59999999999999</v>
+        <v>73.59</v>
       </c>
       <c r="F209">
         <v>70.63</v>
       </c>
       <c r="G209">
-        <v>56.63</v>
+        <v>56.62</v>
       </c>
       <c r="H209">
         <v>0.6</v>
@@ -7719,32 +8424,32 @@
       <c r="A210">
         <v>49021</v>
       </c>
-      <c r="B210">
-        <v>2014</v>
-      </c>
-      <c r="C210">
-        <v>11</v>
-      </c>
-      <c r="D210">
-        <v>41.64</v>
+      <c r="B210" t="s">
+        <v>11</v>
+      </c>
+      <c r="C210" t="s">
+        <v>210</v>
+      </c>
+      <c r="D210" t="s">
+        <v>229</v>
       </c>
       <c r="E210">
-        <v>55.18</v>
+        <v>61.030000000000001</v>
       </c>
       <c r="F210">
-        <v>54.23</v>
+        <v>59.45</v>
       </c>
       <c r="G210">
-        <v>33.81</v>
+        <v>39.22</v>
       </c>
       <c r="H210">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="I210">
-        <v>16.8</v>
+        <v>17.3</v>
       </c>
       <c r="J210">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K210">
         <v>0</v>
@@ -7754,23 +8459,23 @@
       <c r="A211">
         <v>49001</v>
       </c>
-      <c r="B211">
-        <v>2014</v>
-      </c>
-      <c r="C211">
-        <v>12</v>
-      </c>
-      <c r="D211">
-        <v>46.29</v>
+      <c r="B211" t="s">
+        <v>11</v>
+      </c>
+      <c r="C211" t="s">
+        <v>230</v>
+      </c>
+      <c r="D211" t="s">
+        <v>231</v>
       </c>
       <c r="E211">
-        <v>86.45999999999999</v>
+        <v>86.48</v>
       </c>
       <c r="F211">
-        <v>81.34999999999999</v>
+        <v>81.34</v>
       </c>
       <c r="G211">
-        <v>79.53</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="H211">
         <v>0.5</v>
@@ -7789,32 +8494,32 @@
       <c r="A212">
         <v>49002</v>
       </c>
-      <c r="B212">
-        <v>2014</v>
-      </c>
-      <c r="C212">
-        <v>12</v>
-      </c>
-      <c r="D212">
-        <v>49.84</v>
+      <c r="B212" t="s">
+        <v>11</v>
+      </c>
+      <c r="C212" t="s">
+        <v>230</v>
+      </c>
+      <c r="D212" t="s">
+        <v>232</v>
       </c>
       <c r="E212">
-        <v>97.8</v>
+        <v>93.61</v>
       </c>
       <c r="F212">
-        <v>90.81999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="G212">
-        <v>93.33</v>
+        <v>88.37</v>
       </c>
       <c r="H212">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I212">
         <v>10.3</v>
       </c>
       <c r="J212">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K212">
         <v>0</v>
@@ -7824,26 +8529,26 @@
       <c r="A213">
         <v>49003</v>
       </c>
-      <c r="B213">
-        <v>2014</v>
-      </c>
-      <c r="C213">
-        <v>12</v>
-      </c>
-      <c r="D213">
-        <v>49.88</v>
+      <c r="B213" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213" t="s">
+        <v>230</v>
+      </c>
+      <c r="D213" t="s">
+        <v>211</v>
       </c>
       <c r="E213">
-        <v>96.89</v>
+        <v>90.66</v>
       </c>
       <c r="F213">
-        <v>90.45999999999999</v>
+        <v>85.38</v>
       </c>
       <c r="G213">
-        <v>93.18000000000001</v>
+        <v>80.75</v>
       </c>
       <c r="H213">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I213">
         <v>13.2</v>
@@ -7859,32 +8564,32 @@
       <c r="A214">
         <v>49004</v>
       </c>
-      <c r="B214">
-        <v>2014</v>
-      </c>
-      <c r="C214">
-        <v>12</v>
-      </c>
-      <c r="D214">
-        <v>45.99</v>
+      <c r="B214" t="s">
+        <v>11</v>
+      </c>
+      <c r="C214" t="s">
+        <v>230</v>
+      </c>
+      <c r="D214" t="s">
+        <v>233</v>
       </c>
       <c r="E214">
-        <v>80.79000000000001</v>
+        <v>90.52</v>
       </c>
       <c r="F214">
-        <v>76.98</v>
+        <v>85.019999999999996</v>
       </c>
       <c r="G214">
-        <v>68.84</v>
+        <v>83.92</v>
       </c>
       <c r="H214">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="I214">
         <v>13.2</v>
       </c>
       <c r="J214">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K214">
         <v>0</v>
@@ -7894,32 +8599,32 @@
       <c r="A215">
         <v>49005</v>
       </c>
-      <c r="B215">
-        <v>2014</v>
-      </c>
-      <c r="C215">
-        <v>12</v>
-      </c>
-      <c r="D215">
-        <v>46.93</v>
+      <c r="B215" t="s">
+        <v>11</v>
+      </c>
+      <c r="C215" t="s">
+        <v>230</v>
+      </c>
+      <c r="D215" t="s">
+        <v>234</v>
       </c>
       <c r="E215">
-        <v>88.43000000000001</v>
+        <v>90.010000000000005</v>
       </c>
       <c r="F215">
-        <v>82.84</v>
+        <v>84.099999999999994</v>
       </c>
       <c r="G215">
-        <v>80.030000000000001</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="H215">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I215">
         <v>13.2</v>
       </c>
       <c r="J215">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K215">
         <v>0</v>
@@ -7929,17 +8634,17 @@
       <c r="A216">
         <v>49006</v>
       </c>
-      <c r="B216">
-        <v>2014</v>
-      </c>
-      <c r="C216">
-        <v>12</v>
-      </c>
-      <c r="D216">
-        <v>45.94</v>
+      <c r="B216" t="s">
+        <v>11</v>
+      </c>
+      <c r="C216" t="s">
+        <v>230</v>
+      </c>
+      <c r="D216" t="s">
+        <v>235</v>
       </c>
       <c r="E216">
-        <v>84.59999999999999</v>
+        <v>84.53</v>
       </c>
       <c r="F216">
         <v>80.19</v>
@@ -7964,29 +8669,29 @@
       <c r="A217">
         <v>49007</v>
       </c>
-      <c r="B217">
-        <v>2014</v>
-      </c>
-      <c r="C217">
-        <v>12</v>
-      </c>
-      <c r="D217">
-        <v>45.41</v>
+      <c r="B217" t="s">
+        <v>11</v>
+      </c>
+      <c r="C217" t="s">
+        <v>230</v>
+      </c>
+      <c r="D217" t="s">
+        <v>236</v>
       </c>
       <c r="E217">
-        <v>85.049999999999997</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="F217">
-        <v>79.73999999999999</v>
+        <v>83.099999999999994</v>
       </c>
       <c r="G217">
-        <v>78.0</v>
+        <v>83.33</v>
       </c>
       <c r="H217">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="I217">
-        <v>9.5</v>
+        <v>10.0</v>
       </c>
       <c r="J217">
         <v>36</v>
@@ -7999,14 +8704,14 @@
       <c r="A218">
         <v>49008</v>
       </c>
-      <c r="B218">
-        <v>2014</v>
-      </c>
-      <c r="C218">
-        <v>12</v>
-      </c>
-      <c r="D218">
-        <v>43.85</v>
+      <c r="B218" t="s">
+        <v>11</v>
+      </c>
+      <c r="C218" t="s">
+        <v>230</v>
+      </c>
+      <c r="D218" t="s">
+        <v>237</v>
       </c>
       <c r="E218">
         <v>81.73</v>
@@ -8034,26 +8739,26 @@
       <c r="A219">
         <v>49009</v>
       </c>
-      <c r="B219">
-        <v>2014</v>
-      </c>
-      <c r="C219">
-        <v>12</v>
-      </c>
-      <c r="D219">
-        <v>44.22</v>
+      <c r="B219" t="s">
+        <v>11</v>
+      </c>
+      <c r="C219" t="s">
+        <v>230</v>
+      </c>
+      <c r="D219" t="s">
+        <v>16</v>
       </c>
       <c r="E219">
-        <v>84.17</v>
+        <v>82.36</v>
       </c>
       <c r="F219">
-        <v>78.83</v>
+        <v>77.17</v>
       </c>
       <c r="G219">
-        <v>78.23</v>
+        <v>77.019999999999996</v>
       </c>
       <c r="H219">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="I219">
         <v>9.3</v>
@@ -8069,17 +8774,17 @@
       <c r="A220">
         <v>49010</v>
       </c>
-      <c r="B220">
-        <v>2014</v>
-      </c>
-      <c r="C220">
-        <v>12</v>
-      </c>
-      <c r="D220">
-        <v>45.8</v>
+      <c r="B220" t="s">
+        <v>11</v>
+      </c>
+      <c r="C220" t="s">
+        <v>230</v>
+      </c>
+      <c r="D220" t="s">
+        <v>238</v>
       </c>
       <c r="E220">
-        <v>80.28</v>
+        <v>80.31</v>
       </c>
       <c r="F220">
         <v>76.72</v>
@@ -8104,26 +8809,26 @@
       <c r="A221">
         <v>49011</v>
       </c>
-      <c r="B221">
-        <v>2014</v>
-      </c>
-      <c r="C221">
-        <v>12</v>
-      </c>
-      <c r="D221">
-        <v>43.43</v>
+      <c r="B221" t="s">
+        <v>11</v>
+      </c>
+      <c r="C221" t="s">
+        <v>230</v>
+      </c>
+      <c r="D221" t="s">
+        <v>239</v>
       </c>
       <c r="E221">
-        <v>74.45</v>
+        <v>78.31</v>
       </c>
       <c r="F221">
-        <v>71.40000000000001</v>
+        <v>74.44</v>
       </c>
       <c r="G221">
-        <v>62.020000000000003</v>
+        <v>66.81</v>
       </c>
       <c r="H221">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="I221">
         <v>12.1</v>
@@ -8139,23 +8844,23 @@
       <c r="A222">
         <v>49012</v>
       </c>
-      <c r="B222">
-        <v>2014</v>
-      </c>
-      <c r="C222">
-        <v>12</v>
-      </c>
-      <c r="D222">
-        <v>48.3</v>
+      <c r="B222" t="s">
+        <v>11</v>
+      </c>
+      <c r="C222" t="s">
+        <v>230</v>
+      </c>
+      <c r="D222" t="s">
+        <v>240</v>
       </c>
       <c r="E222">
-        <v>93.83</v>
+        <v>93.86</v>
       </c>
       <c r="F222">
-        <v>87.53</v>
+        <v>87.55</v>
       </c>
       <c r="G222">
-        <v>89.81</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="H222">
         <v>0.45</v>
@@ -8174,23 +8879,23 @@
       <c r="A223">
         <v>49013</v>
       </c>
-      <c r="B223">
-        <v>2014</v>
-      </c>
-      <c r="C223">
-        <v>12</v>
-      </c>
-      <c r="D223">
-        <v>46.53</v>
+      <c r="B223" t="s">
+        <v>11</v>
+      </c>
+      <c r="C223" t="s">
+        <v>230</v>
+      </c>
+      <c r="D223" t="s">
+        <v>241</v>
       </c>
       <c r="E223">
-        <v>85.37</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="F223">
-        <v>80.73999999999999</v>
+        <v>80.75</v>
       </c>
       <c r="G223">
-        <v>77.73999999999999</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="H223">
         <v>0.48</v>
@@ -8209,23 +8914,23 @@
       <c r="A224">
         <v>49014</v>
       </c>
-      <c r="B224">
-        <v>2014</v>
-      </c>
-      <c r="C224">
-        <v>12</v>
-      </c>
-      <c r="D224">
-        <v>46.31</v>
+      <c r="B224" t="s">
+        <v>11</v>
+      </c>
+      <c r="C224" t="s">
+        <v>230</v>
+      </c>
+      <c r="D224" t="s">
+        <v>242</v>
       </c>
       <c r="E224">
-        <v>85.81999999999999</v>
+        <v>85.67</v>
       </c>
       <c r="F224">
-        <v>81.010000000000005</v>
+        <v>80.8</v>
       </c>
       <c r="G224">
-        <v>78.95</v>
+        <v>78.67</v>
       </c>
       <c r="H224">
         <v>0.48</v>
@@ -8244,29 +8949,29 @@
       <c r="A225">
         <v>49017</v>
       </c>
-      <c r="B225">
-        <v>2014</v>
-      </c>
-      <c r="C225">
-        <v>12</v>
-      </c>
-      <c r="D225">
-        <v>45.14</v>
+      <c r="B225" t="s">
+        <v>11</v>
+      </c>
+      <c r="C225" t="s">
+        <v>230</v>
+      </c>
+      <c r="D225" t="s">
+        <v>221</v>
       </c>
       <c r="E225">
-        <v>85.099999999999994</v>
+        <v>80.97</v>
       </c>
       <c r="F225">
-        <v>79.72</v>
+        <v>76.45</v>
       </c>
       <c r="G225">
-        <v>78.84999999999999</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="H225">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="I225">
-        <v>11.2</v>
+        <v>8.8</v>
       </c>
       <c r="J225">
         <v>36</v>
@@ -8279,29 +8984,29 @@
       <c r="A226">
         <v>49018</v>
       </c>
-      <c r="B226">
-        <v>2014</v>
-      </c>
-      <c r="C226">
-        <v>12</v>
-      </c>
-      <c r="D226">
-        <v>47.82</v>
+      <c r="B226" t="s">
+        <v>11</v>
+      </c>
+      <c r="C226" t="s">
+        <v>230</v>
+      </c>
+      <c r="D226" t="s">
+        <v>243</v>
       </c>
       <c r="E226">
-        <v>91.81999999999999</v>
+        <v>91.67</v>
       </c>
       <c r="F226">
-        <v>86.030000000000001</v>
+        <v>85.87</v>
       </c>
       <c r="G226">
-        <v>87.42</v>
+        <v>86.81</v>
       </c>
       <c r="H226">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="I226">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="J226">
         <v>36</v>
@@ -8314,32 +9019,32 @@
       <c r="A227">
         <v>49019</v>
       </c>
-      <c r="B227">
-        <v>2014</v>
-      </c>
-      <c r="C227">
-        <v>12</v>
-      </c>
-      <c r="D227">
-        <v>44.68</v>
+      <c r="B227" t="s">
+        <v>11</v>
+      </c>
+      <c r="C227" t="s">
+        <v>230</v>
+      </c>
+      <c r="D227" t="s">
+        <v>15</v>
       </c>
       <c r="E227">
-        <v>77.42</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F227">
-        <v>74.42</v>
+        <v>75.010000000000005</v>
       </c>
       <c r="G227">
-        <v>65.84999999999999</v>
+        <v>67.25</v>
       </c>
       <c r="H227">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="I227">
         <v>9.5</v>
       </c>
       <c r="J227">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K227">
         <v>0</v>
@@ -8349,23 +9054,23 @@
       <c r="A228">
         <v>49020</v>
       </c>
-      <c r="B228">
-        <v>2014</v>
-      </c>
-      <c r="C228">
-        <v>12</v>
-      </c>
-      <c r="D228">
-        <v>48.65</v>
+      <c r="B228" t="s">
+        <v>11</v>
+      </c>
+      <c r="C228" t="s">
+        <v>230</v>
+      </c>
+      <c r="D228" t="s">
+        <v>244</v>
       </c>
       <c r="E228">
-        <v>93.76000000000001</v>
+        <v>93.75</v>
       </c>
       <c r="F228">
         <v>87.73999999999999</v>
       </c>
       <c r="G228">
-        <v>89.0</v>
+        <v>88.98</v>
       </c>
       <c r="H228">
         <v>0.46</v>
@@ -8384,32 +9089,32 @@
       <c r="A229">
         <v>49021</v>
       </c>
-      <c r="B229">
-        <v>2014</v>
-      </c>
-      <c r="C229">
-        <v>12</v>
-      </c>
-      <c r="D229">
-        <v>39.67</v>
+      <c r="B229" t="s">
+        <v>11</v>
+      </c>
+      <c r="C229" t="s">
+        <v>230</v>
+      </c>
+      <c r="D229" t="s">
+        <v>245</v>
       </c>
       <c r="E229">
-        <v>65.28</v>
+        <v>83.3</v>
       </c>
       <c r="F229">
-        <v>63.11</v>
+        <v>79.11</v>
       </c>
       <c r="G229">
-        <v>53.85</v>
+        <v>74.11</v>
       </c>
       <c r="H229">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="I229">
-        <v>12.0</v>
+        <v>12.8</v>
       </c>
       <c r="J229">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K229">
         <v>0</v>
